--- a/GPR_Events.xlsx
+++ b/GPR_Events.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c17c87fde5f3bec7/Documents/GitHub/Geopolitical-Risk-Bitcoin-SA-Markets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{08A453D2-2E06-4980-A1E9-912DA4BDCD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA42DCDF-4D60-4C77-BCEA-1DAE7314F5C4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{383874F8-BE85-4085-9713-C70562148CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="45 events" sheetId="1" r:id="rId1"/>
     <sheet name="135 Raw Peak Audit" sheetId="2" r:id="rId2"/>
     <sheet name="Sources" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="317">
   <si>
     <t>Event_ID</t>
   </si>
@@ -767,9 +767,6 @@
     <t>https://www.theguardian.com/world/2016/dec/30/syria-ceasefire-remains-intact-despite-apparent-government-violations</t>
   </si>
   <si>
-    <t>The 13 December Guardian report covers the eastern Aleppo evacuation crisis; the 30 December Guardian report directly covers the nationwide Syria ceasefire. Both linked December developments are retained under this existing source entry.</t>
-  </si>
-  <si>
     <t>Trump blames Ukraine over war with Russia, saying it could have made a deal</t>
   </si>
   <si>
@@ -938,9 +935,6 @@
     <t>Regression_Window_Flag</t>
   </si>
   <si>
-    <t>Ardern says she will not speak Christchurch suspect's name</t>
-  </si>
-  <si>
     <t>E37</t>
   </si>
   <si>
@@ -965,7 +959,55 @@
     <t>https://www.theguardian.com/world/2019/mar/19/new-zealand-shooting-ardern-says-she-will-never-speak-suspects-name</t>
   </si>
   <si>
-    <t>Assigned only to the 19 March 2019 raw peak in GPRD_ACT_31_4. The 15 and 28 February raw peaks remain assigned to E25 (India–Pakistan escalation). The 31-day peak-centred window contains evidence of more than one event.</t>
+    <t>Retained for the 30 December 2016 raw peak covering the Syria ceasefire, with the 13 December Aleppo report retained as broader context. The 21 and 23 December raw peaks were reassigned to the Berlin Christmas market attack/manhunt (E39) after review. The assassination of the Russian ambassador in Ankara also occurred on 19 December; the attribution records the selected news episode, not proof that one story alone drove the aggregate GPR index.</t>
+  </si>
+  <si>
+    <t>Christchurch mosque attacks in New Zealand</t>
+  </si>
+  <si>
+    <t>Christchurch massacre: PM confirms children among shooting victims – as it happened</t>
+  </si>
+  <si>
+    <t>https://www.theguardian.com/world/live/2019/mar/15/christchurch-shooting-injuries-reported-as-police-respond-to-critical-incident-live?filterKeyEvents=false&amp;page=with%3Ablock-5c8b6921e4b016d23425c518</t>
+  </si>
+  <si>
+    <t>The underlying episode is the Christchurch mosque attacks of 15 March 2019. Same-day Guardian coverage is the primary source; the 19 March Ardern article is retained as supporting follow-up. The selected raw peak remains 19 March 2019 in GPRD_ACT_31_4.</t>
+  </si>
+  <si>
+    <t>E38</t>
+  </si>
+  <si>
+    <t>Minya bus attack on Coptic Christians in Egypt</t>
+  </si>
+  <si>
+    <t>Egypt launches raids in Libya after attack on Coptic Christians kills 26</t>
+  </si>
+  <si>
+    <t>https://www.theguardian.com/world/2017/may/26/several-killed-in-attack-on-bus-carrying-coptic-christians-in-egypt</t>
+  </si>
+  <si>
+    <t>Assigned to the 26 May 2017 raw peak in GPRD_ACT_21_3. Same-day Guardian coverage documents the Minya bus attack on Coptic Christians, an ACT-type event. The Qatar News Agency hack remains a separate episode under E10. Because the GPR index aggregates newspaper reporting, this is an audited event attribution rather than proof that one story alone generated the peak.</t>
+  </si>
+  <si>
+    <t>E39</t>
+  </si>
+  <si>
+    <t>Berlin Christmas market attack and manhunt for Anis Amri</t>
+  </si>
+  <si>
+    <t>Berlin Christmas market attack: a graphical guide to what we know so far</t>
+  </si>
+  <si>
+    <t>https://www.theguardian.com/world/2016/dec/21/berlin-christmas-market-attack-a-graphical-guide-to-what-we-know-so-far</t>
+  </si>
+  <si>
+    <t>Berlin attack suspect pledged allegiance to Isis in video – live coverage</t>
+  </si>
+  <si>
+    <t>https://www.theguardian.com/world/live/2016/dec/23/berlin-market-attack-suspect-anis-amri-killed-in-milan-reports-say-live-coverage?page=with%3Ablock-585d2f0ee4b06265ff0d6175</t>
+  </si>
+  <si>
+    <t>Assigned to the 21 and 23 December 2016 raw peaks in the 21- and 31-day ACT specifications. The 21 December Guardian report covers the Berlin market attack and manhunt; the 23 December live coverage reports Anis Amri was shot dead in Milan. The Russian ambassador was also assassinated in Ankara on 19 December, so the GPR peak should not be interpreted as proof that the Berlin story alone drove the index.</t>
   </si>
 </sst>
 </file>
@@ -1269,10 +1311,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2478,15 +2516,15 @@
       </c>
       <c r="K23" cm="1">
         <f t="array" ref="K23">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A23)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="str" cm="1">
         <f t="array" ref="L23">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A23)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E21</v>
+        <v>E39; E21</v>
       </c>
       <c r="M23" t="str" cm="1">
         <f t="array" ref="M23">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A23)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
-        <v>Battle of Aleppo and December Syria ceasefire</v>
+        <v>Berlin Christmas market attack and manhunt for Anis Amri; Battle of Aleppo and December Syria ceasefire</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="28.8">
@@ -2526,11 +2564,11 @@
       </c>
       <c r="L24" t="str" cm="1">
         <f t="array" ref="L24">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A24)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E09; E08; E10</v>
+        <v>E09; E08; E38</v>
       </c>
       <c r="M24" t="str" cm="1">
         <f t="array" ref="M24">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A24)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
-        <v>Qatar diplomatic crisis begins as neighbouring states sever ties; Islamic State attacks on Iran's parliament and Khomeini shrine; Qatar News Agency hack that preceded the Qatar diplomatic crisis</v>
+        <v>Qatar diplomatic crisis begins as neighbouring states sever ties; Islamic State attacks on Iran's parliament and Khomeini shrine; Minya bus attack on Coptic Christians in Egypt</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="28.8">
@@ -2742,15 +2780,15 @@
       </c>
       <c r="K29" cm="1">
         <f t="array" ref="K29">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A29)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A29)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E21</v>
+        <v>E39; E21</v>
       </c>
       <c r="M29" t="str" cm="1">
         <f t="array" ref="M29">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A29)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
-        <v>Battle of Aleppo and December Syria ceasefire</v>
+        <v>Berlin Christmas market attack and manhunt for Anis Amri; Battle of Aleppo and December Syria ceasefire</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="28.8">
@@ -2794,7 +2832,7 @@
       </c>
       <c r="M30" t="str" cm="1">
         <f t="array" ref="M30">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A30)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
-        <v>India–Pakistan escalation from Pulwama through the Balakot airstrike; Ardern says she will not speak Christchurch suspect's name</v>
+        <v>India–Pakistan escalation from Pulwama through the Balakot airstrike; Christchurch mosque attacks in New Zealand</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="28.8">
@@ -3561,13 +3599,13 @@
         <v>88</v>
       </c>
       <c r="L1" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="M1" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="N1" s="21" t="s">
         <v>291</v>
-      </c>
-      <c r="N1" s="21" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8">
@@ -3595,8 +3633,8 @@
       <c r="H2" cm="1">
         <v>2</v>
       </c>
-      <c r="I2" s="4" t="str" cm="1">
-        <f t="array" ref="I2">IF(G2="","","E"&amp;TEXT(MATCH(G2,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I2" s="4" t="str">
+        <f>IF(G2="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G2,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E01</v>
       </c>
       <c r="J2" s="18">
@@ -3642,8 +3680,8 @@
       <c r="H3" cm="1">
         <v>2</v>
       </c>
-      <c r="I3" s="4" t="str" cm="1">
-        <f t="array" ref="I3">IF(G3="","","E"&amp;TEXT(MATCH(G3,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I3" s="4" t="str">
+        <f>IF(G3="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G3,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E02</v>
       </c>
       <c r="J3" s="18">
@@ -3689,8 +3727,8 @@
       <c r="H4" cm="1">
         <v>2</v>
       </c>
-      <c r="I4" s="4" t="str" cm="1">
-        <f t="array" ref="I4">IF(G4="","","E"&amp;TEXT(MATCH(G4,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I4" s="4" t="str">
+        <f>IF(G4="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G4,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E02</v>
       </c>
       <c r="J4" s="18">
@@ -3736,8 +3774,8 @@
       <c r="H5" cm="1">
         <v>2</v>
       </c>
-      <c r="I5" s="4" t="str" cm="1">
-        <f t="array" ref="I5">IF(G5="","","E"&amp;TEXT(MATCH(G5,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I5" s="4" t="str">
+        <f>IF(G5="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G5,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J5" s="18">
@@ -3783,8 +3821,8 @@
       <c r="H6" cm="1">
         <v>2</v>
       </c>
-      <c r="I6" s="4" t="str" cm="1">
-        <f t="array" ref="I6">IF(G6="","","E"&amp;TEXT(MATCH(G6,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I6" s="4" t="str">
+        <f>IF(G6="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G6,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J6" s="18">
@@ -3830,8 +3868,8 @@
       <c r="H7" cm="1">
         <v>2</v>
       </c>
-      <c r="I7" s="4" t="str" cm="1">
-        <f t="array" ref="I7">IF(G7="","","E"&amp;TEXT(MATCH(G7,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I7" s="4" t="str">
+        <f>IF(G7="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G7,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J7" s="18">
@@ -3877,8 +3915,8 @@
       <c r="H8" cm="1">
         <v>1</v>
       </c>
-      <c r="I8" s="4" t="str" cm="1">
-        <f t="array" ref="I8">IF(G8="","","E"&amp;TEXT(MATCH(G8,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I8" s="4" t="str">
+        <f>IF(G8="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G8,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J8" s="18">
@@ -3924,8 +3962,8 @@
       <c r="H9" cm="1">
         <v>1</v>
       </c>
-      <c r="I9" s="4" t="str" cm="1">
-        <f t="array" ref="I9">IF(G9="","","E"&amp;TEXT(MATCH(G9,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I9" s="4" t="str">
+        <f>IF(G9="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G9,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J9" s="18">
@@ -3971,8 +4009,8 @@
       <c r="H10" cm="1">
         <v>1</v>
       </c>
-      <c r="I10" s="4" t="str" cm="1">
-        <f t="array" ref="I10">IF(G10="","","E"&amp;TEXT(MATCH(G10,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I10" s="4" t="str">
+        <f>IF(G10="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G10,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J10" s="18">
@@ -4018,8 +4056,8 @@
       <c r="H11" cm="1">
         <v>1</v>
       </c>
-      <c r="I11" s="4" t="str" cm="1">
-        <f t="array" ref="I11">IF(G11="","","E"&amp;TEXT(MATCH(G11,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I11" s="4" t="str">
+        <f>IF(G11="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G11,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J11" s="18">
@@ -4065,8 +4103,8 @@
       <c r="H12" cm="1">
         <v>1</v>
       </c>
-      <c r="I12" s="4" t="str" cm="1">
-        <f t="array" ref="I12">IF(G12="","","E"&amp;TEXT(MATCH(G12,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I12" s="4" t="str">
+        <f>IF(G12="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G12,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J12" s="18">
@@ -4112,8 +4150,8 @@
       <c r="H13" cm="1">
         <v>1</v>
       </c>
-      <c r="I13" s="4" t="str" cm="1">
-        <f t="array" ref="I13">IF(G13="","","E"&amp;TEXT(MATCH(G13,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I13" s="4" t="str">
+        <f>IF(G13="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G13,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J13" s="18">
@@ -4159,8 +4197,8 @@
       <c r="H14" cm="1">
         <v>1</v>
       </c>
-      <c r="I14" s="4" t="str" cm="1">
-        <f t="array" ref="I14">IF(G14="","","E"&amp;TEXT(MATCH(G14,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I14" s="4" t="str">
+        <f>IF(G14="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G14,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J14" s="18">
@@ -4206,8 +4244,8 @@
       <c r="H15" cm="1">
         <v>1</v>
       </c>
-      <c r="I15" s="4" t="str" cm="1">
-        <f t="array" ref="I15">IF(G15="","","E"&amp;TEXT(MATCH(G15,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I15" s="4" t="str">
+        <f>IF(G15="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G15,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J15" s="18">
@@ -4253,8 +4291,8 @@
       <c r="H16" cm="1">
         <v>1</v>
       </c>
-      <c r="I16" s="4" t="str" cm="1">
-        <f t="array" ref="I16">IF(G16="","","E"&amp;TEXT(MATCH(G16,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I16" s="4" t="str">
+        <f>IF(G16="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G16,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J16" s="18">
@@ -4300,8 +4338,8 @@
       <c r="H17" cm="1">
         <v>2</v>
       </c>
-      <c r="I17" s="4" t="str" cm="1">
-        <f t="array" ref="I17">IF(G17="","","E"&amp;TEXT(MATCH(G17,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I17" s="4" t="str">
+        <f>IF(G17="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G17,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J17" s="18">
@@ -4347,8 +4385,8 @@
       <c r="H18" cm="1">
         <v>2</v>
       </c>
-      <c r="I18" s="4" t="str" cm="1">
-        <f t="array" ref="I18">IF(G18="","","E"&amp;TEXT(MATCH(G18,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I18" s="4" t="str">
+        <f>IF(G18="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G18,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J18" s="18">
@@ -4394,8 +4432,8 @@
       <c r="H19" cm="1">
         <v>2</v>
       </c>
-      <c r="I19" s="4" t="str" cm="1">
-        <f t="array" ref="I19">IF(G19="","","E"&amp;TEXT(MATCH(G19,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I19" s="4" t="str">
+        <f>IF(G19="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G19,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J19" s="18">
@@ -4441,8 +4479,8 @@
       <c r="H20" cm="1">
         <v>3</v>
       </c>
-      <c r="I20" s="4" t="str" cm="1">
-        <f t="array" ref="I20">IF(G20="","","E"&amp;TEXT(MATCH(G20,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I20" s="4" t="str">
+        <f>IF(G20="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G20,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E08</v>
       </c>
       <c r="J20" s="18">
@@ -4488,8 +4526,8 @@
       <c r="H21" cm="1">
         <v>3</v>
       </c>
-      <c r="I21" s="4" t="str" cm="1">
-        <f t="array" ref="I21">IF(G21="","","E"&amp;TEXT(MATCH(G21,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I21" s="4" t="str">
+        <f>IF(G21="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G21,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E09</v>
       </c>
       <c r="J21" s="18">
@@ -4535,8 +4573,8 @@
       <c r="H22" cm="1">
         <v>3</v>
       </c>
-      <c r="I22" s="4" t="str" cm="1">
-        <f t="array" ref="I22">IF(G22="","","E"&amp;TEXT(MATCH(G22,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I22" s="4" t="str">
+        <f>IF(G22="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G22,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E10</v>
       </c>
       <c r="J22" s="18">
@@ -4582,8 +4620,8 @@
       <c r="H23" cm="1">
         <v>2</v>
       </c>
-      <c r="I23" s="4" t="str" cm="1">
-        <f t="array" ref="I23">IF(G23="","","E"&amp;TEXT(MATCH(G23,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I23" s="4" t="str">
+        <f>IF(G23="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G23,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E11</v>
       </c>
       <c r="J23" s="18">
@@ -4629,8 +4667,8 @@
       <c r="H24" cm="1">
         <v>2</v>
       </c>
-      <c r="I24" s="4" t="str" cm="1">
-        <f t="array" ref="I24">IF(G24="","","E"&amp;TEXT(MATCH(G24,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I24" s="4" t="str">
+        <f>IF(G24="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G24,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E12</v>
       </c>
       <c r="J24" s="18">
@@ -4676,8 +4714,8 @@
       <c r="H25" cm="1">
         <v>2</v>
       </c>
-      <c r="I25" s="4" t="str" cm="1">
-        <f t="array" ref="I25">IF(G25="","","E"&amp;TEXT(MATCH(G25,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I25" s="4" t="str">
+        <f>IF(G25="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G25,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E12</v>
       </c>
       <c r="J25" s="18">
@@ -4723,8 +4761,8 @@
       <c r="H26" cm="1">
         <v>1</v>
       </c>
-      <c r="I26" s="4" t="str" cm="1">
-        <f t="array" ref="I26">IF(G26="","","E"&amp;TEXT(MATCH(G26,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I26" s="4" t="str">
+        <f>IF(G26="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G26,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E13</v>
       </c>
       <c r="J26" s="18">
@@ -4770,8 +4808,8 @@
       <c r="H27" cm="1">
         <v>1</v>
       </c>
-      <c r="I27" s="4" t="str" cm="1">
-        <f t="array" ref="I27">IF(G27="","","E"&amp;TEXT(MATCH(G27,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I27" s="4" t="str">
+        <f>IF(G27="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G27,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E13</v>
       </c>
       <c r="J27" s="18">
@@ -4817,8 +4855,8 @@
       <c r="H28" cm="1">
         <v>1</v>
       </c>
-      <c r="I28" s="4" t="str" cm="1">
-        <f t="array" ref="I28">IF(G28="","","E"&amp;TEXT(MATCH(G28,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I28" s="4" t="str">
+        <f>IF(G28="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G28,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E13</v>
       </c>
       <c r="J28" s="18">
@@ -4864,8 +4902,8 @@
       <c r="H29" cm="1">
         <v>2</v>
       </c>
-      <c r="I29" s="4" t="str" cm="1">
-        <f t="array" ref="I29">IF(G29="","","E"&amp;TEXT(MATCH(G29,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I29" s="4" t="str">
+        <f>IF(G29="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G29,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J29" s="18">
@@ -4911,8 +4949,8 @@
       <c r="H30" cm="1">
         <v>2</v>
       </c>
-      <c r="I30" s="4" t="str" cm="1">
-        <f t="array" ref="I30">IF(G30="","","E"&amp;TEXT(MATCH(G30,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I30" s="4" t="str">
+        <f>IF(G30="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G30,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J30" s="18">
@@ -4958,8 +4996,8 @@
       <c r="H31" cm="1">
         <v>2</v>
       </c>
-      <c r="I31" s="4" t="str" cm="1">
-        <f t="array" ref="I31">IF(G31="","","E"&amp;TEXT(MATCH(G31,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I31" s="4" t="str">
+        <f>IF(G31="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G31,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E14</v>
       </c>
       <c r="J31" s="18">
@@ -5005,8 +5043,8 @@
       <c r="H32" cm="1">
         <v>2</v>
       </c>
-      <c r="I32" s="4" t="str" cm="1">
-        <f t="array" ref="I32">IF(G32="","","E"&amp;TEXT(MATCH(G32,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I32" s="4" t="str">
+        <f>IF(G32="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G32,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E15</v>
       </c>
       <c r="J32" s="18">
@@ -5052,8 +5090,8 @@
       <c r="H33" cm="1">
         <v>2</v>
       </c>
-      <c r="I33" s="4" t="str" cm="1">
-        <f t="array" ref="I33">IF(G33="","","E"&amp;TEXT(MATCH(G33,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I33" s="4" t="str">
+        <f>IF(G33="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G33,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J33" s="18">
@@ -5099,8 +5137,8 @@
       <c r="H34" cm="1">
         <v>2</v>
       </c>
-      <c r="I34" s="4" t="str" cm="1">
-        <f t="array" ref="I34">IF(G34="","","E"&amp;TEXT(MATCH(G34,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I34" s="4" t="str">
+        <f>IF(G34="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G34,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J34" s="18">
@@ -5146,8 +5184,8 @@
       <c r="H35" cm="1">
         <v>1</v>
       </c>
-      <c r="I35" s="4" t="str" cm="1">
-        <f t="array" ref="I35">IF(G35="","","E"&amp;TEXT(MATCH(G35,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I35" s="4" t="str">
+        <f>IF(G35="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G35,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J35" s="18">
@@ -5193,8 +5231,8 @@
       <c r="H36" cm="1">
         <v>1</v>
       </c>
-      <c r="I36" s="4" t="str" cm="1">
-        <f t="array" ref="I36">IF(G36="","","E"&amp;TEXT(MATCH(G36,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I36" s="4" t="str">
+        <f>IF(G36="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G36,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J36" s="18">
@@ -5240,8 +5278,8 @@
       <c r="H37" cm="1">
         <v>1</v>
       </c>
-      <c r="I37" s="4" t="str" cm="1">
-        <f t="array" ref="I37">IF(G37="","","E"&amp;TEXT(MATCH(G37,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I37" s="4" t="str">
+        <f>IF(G37="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G37,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J37" s="18">
@@ -5287,8 +5325,8 @@
       <c r="H38" cm="1">
         <v>1</v>
       </c>
-      <c r="I38" s="4" t="str" cm="1">
-        <f t="array" ref="I38">IF(G38="","","E"&amp;TEXT(MATCH(G38,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I38" s="4" t="str">
+        <f>IF(G38="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G38,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E16</v>
       </c>
       <c r="J38" s="18">
@@ -5334,8 +5372,8 @@
       <c r="H39" cm="1">
         <v>1</v>
       </c>
-      <c r="I39" s="4" t="str" cm="1">
-        <f t="array" ref="I39">IF(G39="","","E"&amp;TEXT(MATCH(G39,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I39" s="4" t="str">
+        <f>IF(G39="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G39,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E16</v>
       </c>
       <c r="J39" s="18">
@@ -5381,8 +5419,8 @@
       <c r="H40" cm="1">
         <v>1</v>
       </c>
-      <c r="I40" s="4" t="str" cm="1">
-        <f t="array" ref="I40">IF(G40="","","E"&amp;TEXT(MATCH(G40,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I40" s="4" t="str">
+        <f>IF(G40="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G40,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E16</v>
       </c>
       <c r="J40" s="18">
@@ -5428,8 +5466,8 @@
       <c r="H41" cm="1">
         <v>1</v>
       </c>
-      <c r="I41" s="4" t="str" cm="1">
-        <f t="array" ref="I41">IF(G41="","","E"&amp;TEXT(MATCH(G41,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I41" s="4" t="str">
+        <f>IF(G41="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G41,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J41" s="18">
@@ -5475,8 +5513,8 @@
       <c r="H42" cm="1">
         <v>1</v>
       </c>
-      <c r="I42" s="4" t="str" cm="1">
-        <f t="array" ref="I42">IF(G42="","","E"&amp;TEXT(MATCH(G42,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I42" s="4" t="str">
+        <f>IF(G42="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G42,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J42" s="18">
@@ -5522,8 +5560,8 @@
       <c r="H43" cm="1">
         <v>1</v>
       </c>
-      <c r="I43" s="4" t="str" cm="1">
-        <f t="array" ref="I43">IF(G43="","","E"&amp;TEXT(MATCH(G43,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I43" s="4" t="str">
+        <f>IF(G43="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G43,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J43" s="18">
@@ -5569,8 +5607,8 @@
       <c r="H44" cm="1">
         <v>2</v>
       </c>
-      <c r="I44" s="4" t="str" cm="1">
-        <f t="array" ref="I44">IF(G44="","","E"&amp;TEXT(MATCH(G44,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I44" s="4" t="str">
+        <f>IF(G44="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G44,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J44" s="18">
@@ -5616,8 +5654,8 @@
       <c r="H45" cm="1">
         <v>2</v>
       </c>
-      <c r="I45" s="4" t="str" cm="1">
-        <f t="array" ref="I45">IF(G45="","","E"&amp;TEXT(MATCH(G45,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I45" s="4" t="str">
+        <f>IF(G45="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G45,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J45" s="18">
@@ -5663,8 +5701,8 @@
       <c r="H46" cm="1">
         <v>2</v>
       </c>
-      <c r="I46" s="4" t="str" cm="1">
-        <f t="array" ref="I46">IF(G46="","","E"&amp;TEXT(MATCH(G46,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I46" s="4" t="str">
+        <f>IF(G46="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G46,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E14</v>
       </c>
       <c r="J46" s="18">
@@ -5710,8 +5748,8 @@
       <c r="H47" cm="1">
         <v>2</v>
       </c>
-      <c r="I47" s="4" t="str" cm="1">
-        <f t="array" ref="I47">IF(G47="","","E"&amp;TEXT(MATCH(G47,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I47" s="4" t="str">
+        <f>IF(G47="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G47,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J47" s="18">
@@ -5757,8 +5795,8 @@
       <c r="H48" cm="1">
         <v>2</v>
       </c>
-      <c r="I48" s="4" t="str" cm="1">
-        <f t="array" ref="I48">IF(G48="","","E"&amp;TEXT(MATCH(G48,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I48" s="4" t="str">
+        <f>IF(G48="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G48,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J48" s="18">
@@ -5804,8 +5842,8 @@
       <c r="H49" cm="1">
         <v>2</v>
       </c>
-      <c r="I49" s="4" t="str" cm="1">
-        <f t="array" ref="I49">IF(G49="","","E"&amp;TEXT(MATCH(G49,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I49" s="4" t="str">
+        <f>IF(G49="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G49,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J49" s="18">
@@ -5851,8 +5889,8 @@
       <c r="H50" cm="1">
         <v>2</v>
       </c>
-      <c r="I50" s="4" t="str" cm="1">
-        <f t="array" ref="I50">IF(G50="","","E"&amp;TEXT(MATCH(G50,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I50" s="4" t="str">
+        <f>IF(G50="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G50,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E18</v>
       </c>
       <c r="J50" s="18">
@@ -5898,8 +5936,8 @@
       <c r="H51" cm="1">
         <v>2</v>
       </c>
-      <c r="I51" s="4" t="str" cm="1">
-        <f t="array" ref="I51">IF(G51="","","E"&amp;TEXT(MATCH(G51,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I51" s="4" t="str">
+        <f>IF(G51="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G51,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E19</v>
       </c>
       <c r="J51" s="18">
@@ -5945,8 +5983,8 @@
       <c r="H52" cm="1">
         <v>2</v>
       </c>
-      <c r="I52" s="4" t="str" cm="1">
-        <f t="array" ref="I52">IF(G52="","","E"&amp;TEXT(MATCH(G52,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I52" s="4" t="str">
+        <f>IF(G52="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G52,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E18</v>
       </c>
       <c r="J52" s="18">
@@ -5992,8 +6030,8 @@
       <c r="H53" cm="1">
         <v>2</v>
       </c>
-      <c r="I53" s="4" t="str" cm="1">
-        <f t="array" ref="I53">IF(G53="","","E"&amp;TEXT(MATCH(G53,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I53" s="4" t="str">
+        <f>IF(G53="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G53,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E20</v>
       </c>
       <c r="J53" s="18">
@@ -6039,8 +6077,8 @@
       <c r="H54" cm="1">
         <v>2</v>
       </c>
-      <c r="I54" s="4" t="str" cm="1">
-        <f t="array" ref="I54">IF(G54="","","E"&amp;TEXT(MATCH(G54,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I54" s="4" t="str">
+        <f>IF(G54="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G54,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J54" s="18">
@@ -6086,8 +6124,8 @@
       <c r="H55" cm="1">
         <v>2</v>
       </c>
-      <c r="I55" s="4" t="str" cm="1">
-        <f t="array" ref="I55">IF(G55="","","E"&amp;TEXT(MATCH(G55,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I55" s="4" t="str">
+        <f>IF(G55="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G55,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E20</v>
       </c>
       <c r="J55" s="18">
@@ -6133,8 +6171,8 @@
       <c r="H56" cm="1">
         <v>1</v>
       </c>
-      <c r="I56" s="4" t="str" cm="1">
-        <f t="array" ref="I56">IF(G56="","","E"&amp;TEXT(MATCH(G56,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I56" s="4" t="str">
+        <f>IF(G56="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G56,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J56" s="18">
@@ -6180,8 +6218,8 @@
       <c r="H57" cm="1">
         <v>1</v>
       </c>
-      <c r="I57" s="4" t="str" cm="1">
-        <f t="array" ref="I57">IF(G57="","","E"&amp;TEXT(MATCH(G57,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I57" s="4" t="str">
+        <f>IF(G57="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G57,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J57" s="18">
@@ -6227,8 +6265,8 @@
       <c r="H58" cm="1">
         <v>1</v>
       </c>
-      <c r="I58" s="4" t="str" cm="1">
-        <f t="array" ref="I58">IF(G58="","","E"&amp;TEXT(MATCH(G58,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I58" s="4" t="str">
+        <f>IF(G58="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G58,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J58" s="18">
@@ -6274,8 +6312,8 @@
       <c r="H59" cm="1">
         <v>1</v>
       </c>
-      <c r="I59" s="4" t="str" cm="1">
-        <f t="array" ref="I59">IF(G59="","","E"&amp;TEXT(MATCH(G59,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I59" s="4" t="str">
+        <f>IF(G59="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G59,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J59" s="18">
@@ -6321,8 +6359,8 @@
       <c r="H60" cm="1">
         <v>1</v>
       </c>
-      <c r="I60" s="4" t="str" cm="1">
-        <f t="array" ref="I60">IF(G60="","","E"&amp;TEXT(MATCH(G60,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I60" s="4" t="str">
+        <f>IF(G60="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G60,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J60" s="18">
@@ -6368,8 +6406,8 @@
       <c r="H61" cm="1">
         <v>1</v>
       </c>
-      <c r="I61" s="4" t="str" cm="1">
-        <f t="array" ref="I61">IF(G61="","","E"&amp;TEXT(MATCH(G61,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I61" s="4" t="str">
+        <f>IF(G61="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G61,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J61" s="18">
@@ -6415,8 +6453,8 @@
       <c r="H62" cm="1">
         <v>2</v>
       </c>
-      <c r="I62" s="4" t="str" cm="1">
-        <f t="array" ref="I62">IF(G62="","","E"&amp;TEXT(MATCH(G62,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I62" s="4" t="str">
+        <f>IF(G62="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G62,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J62" s="18">
@@ -6462,8 +6500,8 @@
       <c r="H63" cm="1">
         <v>2</v>
       </c>
-      <c r="I63" s="4" t="str" cm="1">
-        <f t="array" ref="I63">IF(G63="","","E"&amp;TEXT(MATCH(G63,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I63" s="4" t="str">
+        <f>IF(G63="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G63,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J63" s="18">
@@ -6509,8 +6547,8 @@
       <c r="H64" cm="1">
         <v>2</v>
       </c>
-      <c r="I64" s="4" t="str" cm="1">
-        <f t="array" ref="I64">IF(G64="","","E"&amp;TEXT(MATCH(G64,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I64" s="4" t="str">
+        <f>IF(G64="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G64,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J64" s="18">
@@ -6551,17 +6589,17 @@
         <v>311.33465576171898</v>
       </c>
       <c r="G65" s="15" t="s">
-        <v>48</v>
+        <v>311</v>
       </c>
       <c r="H65" cm="1">
-        <v>1</v>
-      </c>
-      <c r="I65" s="4" t="str" cm="1">
-        <f t="array" ref="I65">IF(G65="","","E"&amp;TEXT(MATCH(G65,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
-        <v>E21</v>
+        <v>2</v>
+      </c>
+      <c r="I65" s="4" t="str">
+        <f>IF(G65="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G65,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <v>E39</v>
       </c>
       <c r="J65" s="18">
-        <v>42717</v>
+        <v>42723</v>
       </c>
       <c r="K65" s="17" t="str">
         <f t="shared" si="0"/>
@@ -6601,10 +6639,10 @@
         <v>48</v>
       </c>
       <c r="H66" cm="1">
-        <v>1</v>
-      </c>
-      <c r="I66" s="4" t="str" cm="1">
-        <f t="array" ref="I66">IF(G66="","","E"&amp;TEXT(MATCH(G66,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+        <v>2</v>
+      </c>
+      <c r="I66" s="4" t="str">
+        <f>IF(G66="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G66,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E21</v>
       </c>
       <c r="J66" s="18">
@@ -6645,17 +6683,17 @@
         <v>246.60563659668</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>48</v>
+        <v>311</v>
       </c>
       <c r="H67" cm="1">
-        <v>1</v>
-      </c>
-      <c r="I67" s="4" t="str" cm="1">
-        <f t="array" ref="I67">IF(G67="","","E"&amp;TEXT(MATCH(G67,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
-        <v>E21</v>
+        <v>2</v>
+      </c>
+      <c r="I67" s="4" t="str">
+        <f>IF(G67="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G67,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <v>E39</v>
       </c>
       <c r="J67" s="18">
-        <v>42717</v>
+        <v>42723</v>
       </c>
       <c r="K67" s="17" t="str">
         <f t="shared" si="2"/>
@@ -6697,8 +6735,8 @@
       <c r="H68" cm="1">
         <v>3</v>
       </c>
-      <c r="I68" s="4" t="str" cm="1">
-        <f t="array" ref="I68">IF(G68="","","E"&amp;TEXT(MATCH(G68,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I68" s="4" t="str">
+        <f>IF(G68="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G68,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E09</v>
       </c>
       <c r="J68" s="18">
@@ -6744,8 +6782,8 @@
       <c r="H69" cm="1">
         <v>3</v>
       </c>
-      <c r="I69" s="4" t="str" cm="1">
-        <f t="array" ref="I69">IF(G69="","","E"&amp;TEXT(MATCH(G69,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I69" s="4" t="str">
+        <f>IF(G69="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G69,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E08</v>
       </c>
       <c r="J69" s="18">
@@ -6766,7 +6804,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="43.2">
+    <row r="70" spans="1:14" ht="28.8">
       <c r="A70" s="11" t="s">
         <v>49</v>
       </c>
@@ -6786,17 +6824,17 @@
         <v>289.86331176757801</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>101</v>
+        <v>306</v>
       </c>
       <c r="H70" cm="1">
         <v>3</v>
       </c>
-      <c r="I70" s="4" t="str" cm="1">
-        <f t="array" ref="I70">IF(G70="","","E"&amp;TEXT(MATCH(G70,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
-        <v>E10</v>
+      <c r="I70" s="4" t="str">
+        <f>IF(G70="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G70,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <v>E38</v>
       </c>
       <c r="J70" s="18">
-        <v>42879</v>
+        <v>42881</v>
       </c>
       <c r="K70" s="17" t="str">
         <f t="shared" si="2"/>
@@ -6838,8 +6876,8 @@
       <c r="H71" cm="1">
         <v>2</v>
       </c>
-      <c r="I71" s="4" t="str" cm="1">
-        <f t="array" ref="I71">IF(G71="","","E"&amp;TEXT(MATCH(G71,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I71" s="4" t="str">
+        <f>IF(G71="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G71,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E22</v>
       </c>
       <c r="J71" s="18">
@@ -6885,8 +6923,8 @@
       <c r="H72" cm="1">
         <v>2</v>
       </c>
-      <c r="I72" s="4" t="str" cm="1">
-        <f t="array" ref="I72">IF(G72="","","E"&amp;TEXT(MATCH(G72,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I72" s="4" t="str">
+        <f>IF(G72="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G72,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J72" s="18">
@@ -6932,8 +6970,8 @@
       <c r="H73" cm="1">
         <v>2</v>
       </c>
-      <c r="I73" s="4" t="str" cm="1">
-        <f t="array" ref="I73">IF(G73="","","E"&amp;TEXT(MATCH(G73,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I73" s="4" t="str">
+        <f>IF(G73="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G73,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J73" s="18">
@@ -6979,8 +7017,8 @@
       <c r="H74" cm="1">
         <v>2</v>
       </c>
-      <c r="I74" s="4" t="str" cm="1">
-        <f t="array" ref="I74">IF(G74="","","E"&amp;TEXT(MATCH(G74,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I74" s="4" t="str">
+        <f>IF(G74="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G74,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J74" s="18">
@@ -7026,8 +7064,8 @@
       <c r="H75" cm="1">
         <v>2</v>
       </c>
-      <c r="I75" s="4" t="str" cm="1">
-        <f t="array" ref="I75">IF(G75="","","E"&amp;TEXT(MATCH(G75,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I75" s="4" t="str">
+        <f>IF(G75="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G75,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J75" s="18">
@@ -7073,8 +7111,8 @@
       <c r="H76" cm="1">
         <v>2</v>
       </c>
-      <c r="I76" s="4" t="str" cm="1">
-        <f t="array" ref="I76">IF(G76="","","E"&amp;TEXT(MATCH(G76,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I76" s="4" t="str">
+        <f>IF(G76="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G76,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E14</v>
       </c>
       <c r="J76" s="18">
@@ -7120,8 +7158,8 @@
       <c r="H77" cm="1">
         <v>2</v>
       </c>
-      <c r="I77" s="4" t="str" cm="1">
-        <f t="array" ref="I77">IF(G77="","","E"&amp;TEXT(MATCH(G77,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I77" s="4" t="str">
+        <f>IF(G77="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G77,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E23</v>
       </c>
       <c r="J77" s="18">
@@ -7167,8 +7205,8 @@
       <c r="H78" cm="1">
         <v>2</v>
       </c>
-      <c r="I78" s="4" t="str" cm="1">
-        <f t="array" ref="I78">IF(G78="","","E"&amp;TEXT(MATCH(G78,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I78" s="4" t="str">
+        <f>IF(G78="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G78,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E24</v>
       </c>
       <c r="J78" s="18">
@@ -7214,8 +7252,8 @@
       <c r="H79" cm="1">
         <v>2</v>
       </c>
-      <c r="I79" s="4" t="str" cm="1">
-        <f t="array" ref="I79">IF(G79="","","E"&amp;TEXT(MATCH(G79,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I79" s="4" t="str">
+        <f>IF(G79="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G79,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E24</v>
       </c>
       <c r="J79" s="18">
@@ -7261,8 +7299,8 @@
       <c r="H80" cm="1">
         <v>2</v>
       </c>
-      <c r="I80" s="4" t="str" cm="1">
-        <f t="array" ref="I80">IF(G80="","","E"&amp;TEXT(MATCH(G80,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I80" s="4" t="str">
+        <f>IF(G80="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G80,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J80" s="18">
@@ -7308,8 +7346,8 @@
       <c r="H81" cm="1">
         <v>2</v>
       </c>
-      <c r="I81" s="4" t="str" cm="1">
-        <f t="array" ref="I81">IF(G81="","","E"&amp;TEXT(MATCH(G81,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I81" s="4" t="str">
+        <f>IF(G81="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G81,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J81" s="18">
@@ -7355,8 +7393,8 @@
       <c r="H82" cm="1">
         <v>2</v>
       </c>
-      <c r="I82" s="4" t="str" cm="1">
-        <f t="array" ref="I82">IF(G82="","","E"&amp;TEXT(MATCH(G82,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I82" s="4" t="str">
+        <f>IF(G82="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G82,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J82" s="18">
@@ -7397,17 +7435,17 @@
         <v>311.33465576171898</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>48</v>
+        <v>311</v>
       </c>
       <c r="H83" cm="1">
-        <v>1</v>
-      </c>
-      <c r="I83" s="4" t="str" cm="1">
-        <f t="array" ref="I83">IF(G83="","","E"&amp;TEXT(MATCH(G83,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
-        <v>E21</v>
+        <v>2</v>
+      </c>
+      <c r="I83" s="4" t="str">
+        <f>IF(G83="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G83,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <v>E39</v>
       </c>
       <c r="J83" s="18">
-        <v>42717</v>
+        <v>42723</v>
       </c>
       <c r="K83" s="17" t="str">
         <f t="shared" si="2"/>
@@ -7447,10 +7485,10 @@
         <v>48</v>
       </c>
       <c r="H84" cm="1">
-        <v>1</v>
-      </c>
-      <c r="I84" s="4" t="str" cm="1">
-        <f t="array" ref="I84">IF(G84="","","E"&amp;TEXT(MATCH(G84,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+        <v>2</v>
+      </c>
+      <c r="I84" s="4" t="str">
+        <f>IF(G84="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G84,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E21</v>
       </c>
       <c r="J84" s="18">
@@ -7491,17 +7529,17 @@
         <v>246.60563659668</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>48</v>
+        <v>311</v>
       </c>
       <c r="H85" cm="1">
-        <v>1</v>
-      </c>
-      <c r="I85" s="4" t="str" cm="1">
-        <f t="array" ref="I85">IF(G85="","","E"&amp;TEXT(MATCH(G85,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
-        <v>E21</v>
+        <v>2</v>
+      </c>
+      <c r="I85" s="4" t="str">
+        <f>IF(G85="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G85,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <v>E39</v>
       </c>
       <c r="J85" s="18">
-        <v>42717</v>
+        <v>42723</v>
       </c>
       <c r="K85" s="17" t="str">
         <f t="shared" si="2"/>
@@ -7538,13 +7576,13 @@
         <v>165.32522583007801</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H86" cm="1">
         <v>2</v>
       </c>
-      <c r="I86" s="4" t="str" cm="1">
-        <f t="array" ref="I86">IF(G86="","","E"&amp;TEXT(MATCH(G86,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I86" s="4" t="str">
+        <f>IF(G86="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G86,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E25</v>
       </c>
       <c r="J86" s="18">
@@ -7585,13 +7623,13 @@
         <v>153.59866333007801</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H87" cm="1">
         <v>2</v>
       </c>
-      <c r="I87" s="4" t="str" cm="1">
-        <f t="array" ref="I87">IF(G87="","","E"&amp;TEXT(MATCH(G87,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I87" s="4" t="str">
+        <f>IF(G87="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G87,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E25</v>
       </c>
       <c r="J87" s="18">
@@ -7632,17 +7670,17 @@
         <v>142.805252075195</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H88" cm="1">
         <v>2</v>
       </c>
-      <c r="I88" s="4" t="str" cm="1">
-        <f t="array" ref="I88">IF(G88="","","E"&amp;TEXT(MATCH(G88,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I88" s="4" t="str">
+        <f>IF(G88="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G88,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E26</v>
       </c>
       <c r="J88" s="18">
-        <v>43543</v>
+        <v>43539</v>
       </c>
       <c r="K88" s="17" t="str">
         <f t="shared" si="2"/>
@@ -7684,8 +7722,8 @@
       <c r="H89" cm="1">
         <v>2</v>
       </c>
-      <c r="I89" s="4" t="str" cm="1">
-        <f t="array" ref="I89">IF(G89="","","E"&amp;TEXT(MATCH(G89,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I89" s="4" t="str">
+        <f>IF(G89="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G89,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J89" s="18">
@@ -7731,8 +7769,8 @@
       <c r="H90" cm="1">
         <v>2</v>
       </c>
-      <c r="I90" s="4" t="str" cm="1">
-        <f t="array" ref="I90">IF(G90="","","E"&amp;TEXT(MATCH(G90,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I90" s="4" t="str">
+        <f>IF(G90="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G90,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J90" s="18">
@@ -7778,8 +7816,8 @@
       <c r="H91" cm="1">
         <v>2</v>
       </c>
-      <c r="I91" s="4" t="str" cm="1">
-        <f t="array" ref="I91">IF(G91="","","E"&amp;TEXT(MATCH(G91,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I91" s="4" t="str">
+        <f>IF(G91="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G91,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E14</v>
       </c>
       <c r="J91" s="18">
@@ -7825,8 +7863,8 @@
       <c r="H92" cm="1">
         <v>1</v>
       </c>
-      <c r="I92" s="4" t="str" cm="1">
-        <f t="array" ref="I92">IF(G92="","","E"&amp;TEXT(MATCH(G92,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I92" s="4" t="str">
+        <f>IF(G92="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G92,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E27</v>
       </c>
       <c r="J92" s="18">
@@ -7872,8 +7910,8 @@
       <c r="H93" cm="1">
         <v>1</v>
       </c>
-      <c r="I93" s="4" t="str" cm="1">
-        <f t="array" ref="I93">IF(G93="","","E"&amp;TEXT(MATCH(G93,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I93" s="4" t="str">
+        <f>IF(G93="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G93,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E27</v>
       </c>
       <c r="J93" s="18">
@@ -7919,8 +7957,8 @@
       <c r="H94" cm="1">
         <v>1</v>
       </c>
-      <c r="I94" s="4" t="str" cm="1">
-        <f t="array" ref="I94">IF(G94="","","E"&amp;TEXT(MATCH(G94,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I94" s="4" t="str">
+        <f>IF(G94="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G94,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E27</v>
       </c>
       <c r="J94" s="18">
@@ -7966,8 +8004,8 @@
       <c r="H95" cm="1">
         <v>2</v>
       </c>
-      <c r="I95" s="4" t="str" cm="1">
-        <f t="array" ref="I95">IF(G95="","","E"&amp;TEXT(MATCH(G95,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I95" s="4" t="str">
+        <f>IF(G95="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G95,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E19</v>
       </c>
       <c r="J95" s="18">
@@ -8013,8 +8051,8 @@
       <c r="H96" cm="1">
         <v>2</v>
       </c>
-      <c r="I96" s="4" t="str" cm="1">
-        <f t="array" ref="I96">IF(G96="","","E"&amp;TEXT(MATCH(G96,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I96" s="4" t="str">
+        <f>IF(G96="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G96,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E18</v>
       </c>
       <c r="J96" s="18">
@@ -8060,8 +8098,8 @@
       <c r="H97" cm="1">
         <v>2</v>
       </c>
-      <c r="I97" s="4" t="str" cm="1">
-        <f t="array" ref="I97">IF(G97="","","E"&amp;TEXT(MATCH(G97,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I97" s="4" t="str">
+        <f>IF(G97="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G97,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E19</v>
       </c>
       <c r="J97" s="18">
@@ -8107,8 +8145,8 @@
       <c r="H98" cm="1">
         <v>2</v>
       </c>
-      <c r="I98" s="4" t="str" cm="1">
-        <f t="array" ref="I98">IF(G98="","","E"&amp;TEXT(MATCH(G98,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I98" s="4" t="str">
+        <f>IF(G98="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G98,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J98" s="18">
@@ -8154,8 +8192,8 @@
       <c r="H99" cm="1">
         <v>2</v>
       </c>
-      <c r="I99" s="4" t="str" cm="1">
-        <f t="array" ref="I99">IF(G99="","","E"&amp;TEXT(MATCH(G99,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I99" s="4" t="str">
+        <f>IF(G99="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G99,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J99" s="18">
@@ -8201,8 +8239,8 @@
       <c r="H100" cm="1">
         <v>2</v>
       </c>
-      <c r="I100" s="4" t="str" cm="1">
-        <f t="array" ref="I100">IF(G100="","","E"&amp;TEXT(MATCH(G100,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I100" s="4" t="str">
+        <f>IF(G100="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G100,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E20</v>
       </c>
       <c r="J100" s="18">
@@ -8248,8 +8286,8 @@
       <c r="H101" cm="1">
         <v>1</v>
       </c>
-      <c r="I101" s="4" t="str" cm="1">
-        <f t="array" ref="I101">IF(G101="","","E"&amp;TEXT(MATCH(G101,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I101" s="4" t="str">
+        <f>IF(G101="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G101,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E28</v>
       </c>
       <c r="J101" s="18">
@@ -8295,8 +8333,8 @@
       <c r="H102" cm="1">
         <v>1</v>
       </c>
-      <c r="I102" s="4" t="str" cm="1">
-        <f t="array" ref="I102">IF(G102="","","E"&amp;TEXT(MATCH(G102,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I102" s="4" t="str">
+        <f>IF(G102="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G102,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E28</v>
       </c>
       <c r="J102" s="18">
@@ -8342,8 +8380,8 @@
       <c r="H103" cm="1">
         <v>1</v>
       </c>
-      <c r="I103" s="4" t="str" cm="1">
-        <f t="array" ref="I103">IF(G103="","","E"&amp;TEXT(MATCH(G103,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I103" s="4" t="str">
+        <f>IF(G103="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G103,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E28</v>
       </c>
       <c r="J103" s="18">
@@ -8389,8 +8427,8 @@
       <c r="H104" cm="1">
         <v>1</v>
       </c>
-      <c r="I104" s="4" t="str" cm="1">
-        <f t="array" ref="I104">IF(G104="","","E"&amp;TEXT(MATCH(G104,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I104" s="4" t="str">
+        <f>IF(G104="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G104,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J104" s="18">
@@ -8436,8 +8474,8 @@
       <c r="H105" cm="1">
         <v>1</v>
       </c>
-      <c r="I105" s="4" t="str" cm="1">
-        <f t="array" ref="I105">IF(G105="","","E"&amp;TEXT(MATCH(G105,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I105" s="4" t="str">
+        <f>IF(G105="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G105,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J105" s="18">
@@ -8483,8 +8521,8 @@
       <c r="H106" cm="1">
         <v>1</v>
       </c>
-      <c r="I106" s="4" t="str" cm="1">
-        <f t="array" ref="I106">IF(G106="","","E"&amp;TEXT(MATCH(G106,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I106" s="4" t="str">
+        <f>IF(G106="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G106,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J106" s="18">
@@ -8530,8 +8568,8 @@
       <c r="H107" cm="1">
         <v>1</v>
       </c>
-      <c r="I107" s="4" t="str" cm="1">
-        <f t="array" ref="I107">IF(G107="","","E"&amp;TEXT(MATCH(G107,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I107" s="4" t="str">
+        <f>IF(G107="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G107,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E29</v>
       </c>
       <c r="J107" s="18">
@@ -8577,8 +8615,8 @@
       <c r="H108" cm="1">
         <v>1</v>
       </c>
-      <c r="I108" s="4" t="str" cm="1">
-        <f t="array" ref="I108">IF(G108="","","E"&amp;TEXT(MATCH(G108,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I108" s="4" t="str">
+        <f>IF(G108="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G108,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E29</v>
       </c>
       <c r="J108" s="18">
@@ -8624,8 +8662,8 @@
       <c r="H109" cm="1">
         <v>1</v>
       </c>
-      <c r="I109" s="4" t="str" cm="1">
-        <f t="array" ref="I109">IF(G109="","","E"&amp;TEXT(MATCH(G109,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I109" s="4" t="str">
+        <f>IF(G109="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G109,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E29</v>
       </c>
       <c r="J109" s="18">
@@ -8671,8 +8709,8 @@
       <c r="H110" cm="1">
         <v>3</v>
       </c>
-      <c r="I110" s="4" t="str" cm="1">
-        <f t="array" ref="I110">IF(G110="","","E"&amp;TEXT(MATCH(G110,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I110" s="4" t="str">
+        <f>IF(G110="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G110,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E30</v>
       </c>
       <c r="J110" s="18">
@@ -8718,8 +8756,8 @@
       <c r="H111" cm="1">
         <v>3</v>
       </c>
-      <c r="I111" s="4" t="str" cm="1">
-        <f t="array" ref="I111">IF(G111="","","E"&amp;TEXT(MATCH(G111,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I111" s="4" t="str">
+        <f>IF(G111="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G111,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E31</v>
       </c>
       <c r="J111" s="18">
@@ -8765,8 +8803,8 @@
       <c r="H112" cm="1">
         <v>3</v>
       </c>
-      <c r="I112" s="4" t="str" cm="1">
-        <f t="array" ref="I112">IF(G112="","","E"&amp;TEXT(MATCH(G112,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I112" s="4" t="str">
+        <f>IF(G112="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G112,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E32</v>
       </c>
       <c r="J112" s="18">
@@ -8812,8 +8850,8 @@
       <c r="H113" cm="1">
         <v>2</v>
       </c>
-      <c r="I113" s="4" t="str" cm="1">
-        <f t="array" ref="I113">IF(G113="","","E"&amp;TEXT(MATCH(G113,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I113" s="4" t="str">
+        <f>IF(G113="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G113,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J113" s="18">
@@ -8859,8 +8897,8 @@
       <c r="H114" cm="1">
         <v>2</v>
       </c>
-      <c r="I114" s="4" t="str" cm="1">
-        <f t="array" ref="I114">IF(G114="","","E"&amp;TEXT(MATCH(G114,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I114" s="4" t="str">
+        <f>IF(G114="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G114,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J114" s="18">
@@ -8906,8 +8944,8 @@
       <c r="H115" cm="1">
         <v>2</v>
       </c>
-      <c r="I115" s="4" t="str" cm="1">
-        <f t="array" ref="I115">IF(G115="","","E"&amp;TEXT(MATCH(G115,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I115" s="4" t="str">
+        <f>IF(G115="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G115,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J115" s="18">
@@ -8953,8 +8991,8 @@
       <c r="H116" cm="1">
         <v>2</v>
       </c>
-      <c r="I116" s="4" t="str" cm="1">
-        <f t="array" ref="I116">IF(G116="","","E"&amp;TEXT(MATCH(G116,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I116" s="4" t="str">
+        <f>IF(G116="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G116,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E11</v>
       </c>
       <c r="J116" s="18">
@@ -9000,8 +9038,8 @@
       <c r="H117" cm="1">
         <v>2</v>
       </c>
-      <c r="I117" s="4" t="str" cm="1">
-        <f t="array" ref="I117">IF(G117="","","E"&amp;TEXT(MATCH(G117,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I117" s="4" t="str">
+        <f>IF(G117="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G117,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E12</v>
       </c>
       <c r="J117" s="18">
@@ -9047,8 +9085,8 @@
       <c r="H118" cm="1">
         <v>2</v>
       </c>
-      <c r="I118" s="4" t="str" cm="1">
-        <f t="array" ref="I118">IF(G118="","","E"&amp;TEXT(MATCH(G118,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I118" s="4" t="str">
+        <f>IF(G118="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G118,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E11</v>
       </c>
       <c r="J118" s="18">
@@ -9094,8 +9132,8 @@
       <c r="H119" cm="1">
         <v>3</v>
       </c>
-      <c r="I119" s="4" t="str" cm="1">
-        <f t="array" ref="I119">IF(G119="","","E"&amp;TEXT(MATCH(G119,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I119" s="4" t="str">
+        <f>IF(G119="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G119,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E14</v>
       </c>
       <c r="J119" s="18">
@@ -9141,8 +9179,8 @@
       <c r="H120" cm="1">
         <v>3</v>
       </c>
-      <c r="I120" s="4" t="str" cm="1">
-        <f t="array" ref="I120">IF(G120="","","E"&amp;TEXT(MATCH(G120,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I120" s="4" t="str">
+        <f>IF(G120="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G120,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E33</v>
       </c>
       <c r="J120" s="18">
@@ -9188,8 +9226,8 @@
       <c r="H121" cm="1">
         <v>3</v>
       </c>
-      <c r="I121" s="4" t="str" cm="1">
-        <f t="array" ref="I121">IF(G121="","","E"&amp;TEXT(MATCH(G121,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I121" s="4" t="str">
+        <f>IF(G121="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G121,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E34</v>
       </c>
       <c r="J121" s="18">
@@ -9235,8 +9273,8 @@
       <c r="H122" cm="1">
         <v>2</v>
       </c>
-      <c r="I122" s="4" t="str" cm="1">
-        <f t="array" ref="I122">IF(G122="","","E"&amp;TEXT(MATCH(G122,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I122" s="4" t="str">
+        <f>IF(G122="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G122,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E35</v>
       </c>
       <c r="J122" s="18">
@@ -9282,8 +9320,8 @@
       <c r="H123" cm="1">
         <v>2</v>
       </c>
-      <c r="I123" s="4" t="str" cm="1">
-        <f t="array" ref="I123">IF(G123="","","E"&amp;TEXT(MATCH(G123,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I123" s="4" t="str">
+        <f>IF(G123="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G123,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E36</v>
       </c>
       <c r="J123" s="18">
@@ -9329,8 +9367,8 @@
       <c r="H124" cm="1">
         <v>2</v>
       </c>
-      <c r="I124" s="4" t="str" cm="1">
-        <f t="array" ref="I124">IF(G124="","","E"&amp;TEXT(MATCH(G124,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I124" s="4" t="str">
+        <f>IF(G124="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G124,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E36</v>
       </c>
       <c r="J124" s="18">
@@ -9376,8 +9414,8 @@
       <c r="H125" cm="1">
         <v>1</v>
       </c>
-      <c r="I125" s="4" t="str" cm="1">
-        <f t="array" ref="I125">IF(G125="","","E"&amp;TEXT(MATCH(G125,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I125" s="4" t="str">
+        <f>IF(G125="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G125,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E28</v>
       </c>
       <c r="J125" s="18">
@@ -9423,8 +9461,8 @@
       <c r="H126" cm="1">
         <v>1</v>
       </c>
-      <c r="I126" s="4" t="str" cm="1">
-        <f t="array" ref="I126">IF(G126="","","E"&amp;TEXT(MATCH(G126,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I126" s="4" t="str">
+        <f>IF(G126="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G126,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E28</v>
       </c>
       <c r="J126" s="18">
@@ -9470,8 +9508,8 @@
       <c r="H127" cm="1">
         <v>1</v>
       </c>
-      <c r="I127" s="4" t="str" cm="1">
-        <f t="array" ref="I127">IF(G127="","","E"&amp;TEXT(MATCH(G127,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I127" s="4" t="str">
+        <f>IF(G127="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G127,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E28</v>
       </c>
       <c r="J127" s="18">
@@ -9517,8 +9555,8 @@
       <c r="H128" cm="1">
         <v>1</v>
       </c>
-      <c r="I128" s="4" t="str" cm="1">
-        <f t="array" ref="I128">IF(G128="","","E"&amp;TEXT(MATCH(G128,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I128" s="4" t="str">
+        <f>IF(G128="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G128,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E37</v>
       </c>
       <c r="J128" s="18">
@@ -9564,8 +9602,8 @@
       <c r="H129" cm="1">
         <v>1</v>
       </c>
-      <c r="I129" s="4" t="str" cm="1">
-        <f t="array" ref="I129">IF(G129="","","E"&amp;TEXT(MATCH(G129,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I129" s="4" t="str">
+        <f>IF(G129="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G129,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E37</v>
       </c>
       <c r="J129" s="18">
@@ -9611,8 +9649,8 @@
       <c r="H130" cm="1">
         <v>1</v>
       </c>
-      <c r="I130" s="4" t="str" cm="1">
-        <f t="array" ref="I130">IF(G130="","","E"&amp;TEXT(MATCH(G130,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I130" s="4" t="str">
+        <f>IF(G130="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G130,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E37</v>
       </c>
       <c r="J130" s="18">
@@ -9658,8 +9696,8 @@
       <c r="H131" cm="1">
         <v>1</v>
       </c>
-      <c r="I131" s="4" t="str" cm="1">
-        <f t="array" ref="I131">IF(G131="","","E"&amp;TEXT(MATCH(G131,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I131" s="4" t="str">
+        <f>IF(G131="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G131,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J131" s="18">
@@ -9705,8 +9743,8 @@
       <c r="H132" cm="1">
         <v>1</v>
       </c>
-      <c r="I132" s="4" t="str" cm="1">
-        <f t="array" ref="I132">IF(G132="","","E"&amp;TEXT(MATCH(G132,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I132" s="4" t="str">
+        <f>IF(G132="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G132,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J132" s="18">
@@ -9752,8 +9790,8 @@
       <c r="H133" cm="1">
         <v>1</v>
       </c>
-      <c r="I133" s="4" t="str" cm="1">
-        <f t="array" ref="I133">IF(G133="","","E"&amp;TEXT(MATCH(G133,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I133" s="4" t="str">
+        <f>IF(G133="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G133,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E17</v>
       </c>
       <c r="J133" s="18">
@@ -9799,8 +9837,8 @@
       <c r="H134" cm="1">
         <v>3</v>
       </c>
-      <c r="I134" s="4" t="str" cm="1">
-        <f t="array" ref="I134">IF(G134="","","E"&amp;TEXT(MATCH(G134,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I134" s="4" t="str">
+        <f>IF(G134="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G134,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J134" s="18">
@@ -9846,8 +9884,8 @@
       <c r="H135" cm="1">
         <v>3</v>
       </c>
-      <c r="I135" s="4" t="str" cm="1">
-        <f t="array" ref="I135">IF(G135="","","E"&amp;TEXT(MATCH(G135,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I135" s="4" t="str">
+        <f>IF(G135="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G135,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E14</v>
       </c>
       <c r="J135" s="18">
@@ -9893,8 +9931,8 @@
       <c r="H136" cm="1">
         <v>3</v>
       </c>
-      <c r="I136" s="4" t="str" cm="1">
-        <f t="array" ref="I136">IF(G136="","","E"&amp;TEXT(MATCH(G136,_xlfn.UNIQUE(_xlfn._xlws.FILTER($G$2:$G$500,$G$2:$G$500&lt;&gt;"")),0),"00"))</f>
+      <c r="I136" s="4" t="str">
+        <f>IF(G136="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G136,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
         <v>E33</v>
       </c>
       <c r="J136" s="18">
@@ -9922,7 +9960,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -10140,10 +10178,10 @@
         <v>167</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="172.8">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="158.4">
       <c r="A7" s="23" t="s">
         <v>19</v>
       </c>
@@ -10692,7 +10730,7 @@
         <v>235</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="86.7" customHeight="1">
@@ -10712,17 +10750,17 @@
         <v>45707</v>
       </c>
       <c r="F23" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="G23" s="23" t="s">
         <v>237</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>238</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23" s="24"/>
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="70.349999999999994" customHeight="1">
@@ -10736,23 +10774,23 @@
         <v>42017</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E24" s="24">
         <v>42017</v>
       </c>
       <c r="F24" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="G24" s="23" t="s">
         <v>241</v>
-      </c>
-      <c r="G24" s="23" t="s">
-        <v>242</v>
       </c>
       <c r="H24" s="23"/>
       <c r="I24" s="24"/>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="67.5" customHeight="1">
@@ -10772,17 +10810,17 @@
         <v>42019</v>
       </c>
       <c r="F25" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="G25" s="23" t="s">
         <v>244</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>245</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="24"/>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
       <c r="L25" s="23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="65.7" customHeight="1">
@@ -10790,7 +10828,7 @@
         <v>123</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C26" s="24">
         <v>43510</v>
@@ -10802,10 +10840,10 @@
         <v>43510</v>
       </c>
       <c r="F26" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="G26" s="23" t="s">
         <v>248</v>
-      </c>
-      <c r="G26" s="23" t="s">
-        <v>249</v>
       </c>
       <c r="H26" s="23" t="s">
         <v>147</v>
@@ -10814,13 +10852,13 @@
         <v>43529</v>
       </c>
       <c r="J26" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="K26" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="K26" s="23" t="s">
-        <v>251</v>
-      </c>
       <c r="L26" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="48" customHeight="1">
@@ -10828,29 +10866,37 @@
         <v>58</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C27" s="24">
-        <v>43543</v>
+        <v>43539</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>147</v>
       </c>
       <c r="E27" s="24">
+        <v>43539</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="I27" s="24">
         <v>43543</v>
       </c>
-      <c r="F27" s="23" t="s">
-        <v>300</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="H27" s="23"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
+      <c r="J27" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>299</v>
+      </c>
       <c r="L27" s="23" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="48.75" customHeight="1">
@@ -10864,23 +10910,23 @@
         <v>42375</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E28" s="24">
         <v>42375</v>
       </c>
       <c r="F28" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="G28" s="23" t="s">
         <v>253</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>254</v>
       </c>
       <c r="H28" s="23"/>
       <c r="I28" s="24"/>
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="67.95" customHeight="1">
@@ -10894,23 +10940,23 @@
         <v>44616</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E29" s="24">
         <v>44616</v>
       </c>
       <c r="F29" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>256</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>257</v>
       </c>
       <c r="H29" s="23"/>
       <c r="I29" s="24"/>
       <c r="J29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="75.599999999999994" customHeight="1">
@@ -10930,10 +10976,10 @@
         <v>41702</v>
       </c>
       <c r="F30" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="G30" s="23" t="s">
         <v>259</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>260</v>
       </c>
       <c r="H30" s="23" t="s">
         <v>147</v>
@@ -10942,13 +10988,13 @@
         <v>41716</v>
       </c>
       <c r="J30" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="K30" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="K30" s="23" t="s">
+      <c r="L30" s="23" t="s">
         <v>262</v>
-      </c>
-      <c r="L30" s="23" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="51.9" customHeight="1">
@@ -10968,17 +11014,17 @@
         <v>41885</v>
       </c>
       <c r="F31" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>264</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>265</v>
       </c>
       <c r="H31" s="23"/>
       <c r="I31" s="24"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="84.45" customHeight="1">
@@ -10998,17 +11044,17 @@
         <v>41884</v>
       </c>
       <c r="F32" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="G32" s="23" t="s">
         <v>267</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>268</v>
       </c>
       <c r="H32" s="23"/>
       <c r="I32" s="24"/>
       <c r="J32" s="23"/>
       <c r="K32" s="23"/>
       <c r="L32" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="78.75" customHeight="1">
@@ -11028,17 +11074,17 @@
         <v>41859</v>
       </c>
       <c r="F33" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="G33" s="23" t="s">
         <v>270</v>
-      </c>
-      <c r="G33" s="23" t="s">
-        <v>271</v>
       </c>
       <c r="H33" s="23"/>
       <c r="I33" s="24"/>
       <c r="J33" s="23"/>
       <c r="K33" s="23"/>
       <c r="L33" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="67.2" customHeight="1">
@@ -11058,17 +11104,17 @@
         <v>46120</v>
       </c>
       <c r="F34" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="G34" s="23" t="s">
         <v>273</v>
-      </c>
-      <c r="G34" s="23" t="s">
-        <v>274</v>
       </c>
       <c r="H34" s="23"/>
       <c r="I34" s="24"/>
       <c r="J34" s="23"/>
       <c r="K34" s="23"/>
       <c r="L34" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="48.3" customHeight="1">
@@ -11088,10 +11134,10 @@
         <v>46125</v>
       </c>
       <c r="F35" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="G35" s="23" t="s">
         <v>276</v>
-      </c>
-      <c r="G35" s="23" t="s">
-        <v>277</v>
       </c>
       <c r="H35" s="23" t="s">
         <v>147</v>
@@ -11100,13 +11146,13 @@
         <v>46126</v>
       </c>
       <c r="J35" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="K35" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="K35" s="23" t="s">
-        <v>279</v>
-      </c>
       <c r="L35" s="23" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="49.2" customHeight="1">
@@ -11126,10 +11172,10 @@
         <v>42956</v>
       </c>
       <c r="F36" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="G36" s="23" t="s">
         <v>280</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>281</v>
       </c>
       <c r="H36" s="23" t="s">
         <v>147</v>
@@ -11138,13 +11184,13 @@
         <v>42957</v>
       </c>
       <c r="J36" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="K36" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="K36" s="23" t="s">
-        <v>283</v>
-      </c>
       <c r="L36" s="23" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="67.2" customHeight="1">
@@ -11164,22 +11210,22 @@
         <v>42920</v>
       </c>
       <c r="F37" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="G37" s="23" t="s">
         <v>284</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>285</v>
       </c>
       <c r="H37" s="23"/>
       <c r="I37" s="24"/>
       <c r="J37" s="23"/>
       <c r="K37" s="23"/>
       <c r="L37" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="72">
       <c r="A38" s="22" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>77</v>
@@ -11194,17 +11240,85 @@
         <v>44775</v>
       </c>
       <c r="F38" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="G38" s="22" t="s">
         <v>287</v>
-      </c>
-      <c r="G38" s="22" t="s">
-        <v>288</v>
       </c>
       <c r="H38" s="22"/>
       <c r="I38" s="22"/>
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
       <c r="L38" s="27" t="s">
-        <v>289</v>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="187.2">
+      <c r="A39" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C39" s="26">
+        <v>42881</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="26">
+        <v>42881</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>307</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="27" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="216">
+      <c r="A40" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="C40" s="26">
+        <v>42723</v>
+      </c>
+      <c r="D40" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="26">
+        <v>42725</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="G40" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="H40" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="I40" s="22">
+        <v>42727</v>
+      </c>
+      <c r="J40" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="K40" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="L40" s="27" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/GPR_Events.xlsx
+++ b/GPR_Events.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c17c87fde5f3bec7/Documents/GitHub/Geopolitical-Risk-Bitcoin-SA-Markets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{383874F8-BE85-4085-9713-C70562148CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{383874F8-BE85-4085-9713-C70562148CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63E77620-38E4-4E9C-AFEF-585185A54FDA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="45 events" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="309">
   <si>
     <t>Event_ID</t>
   </si>
@@ -362,9 +362,6 @@
     <t>E09</t>
   </si>
   <si>
-    <t>Qatar News Agency hack that preceded the Qatar diplomatic crisis</t>
-  </si>
-  <si>
     <t>E10</t>
   </si>
   <si>
@@ -611,24 +608,6 @@
     <t>Use for the 5–6 June diplomatic-break story, not for the earlier 26 May raw peak; the QNA hack is recorded separately above.</t>
   </si>
   <si>
-    <t>Saudi Arabia and UAE block Qatari media over incendiary statements</t>
-  </si>
-  <si>
-    <t>https://www.theguardian.com/world/2017/may/25/saudi-arabia-and-uae-block-qatari-media-over-incendiary-statements-iran-israel</t>
-  </si>
-  <si>
-    <t>The Guardian (letter by Qatar Government Communications Office)</t>
-  </si>
-  <si>
-    <t>Quotes were falsely attributed to the emir of Qatar and its foreign minister</t>
-  </si>
-  <si>
-    <t>https://www.theguardian.com/world/2017/may/30/quotes-were-falsely-attributed-to-the-emir-of-qatar-and-its-foreign-minister</t>
-  </si>
-  <si>
-    <t>Corrected the story-break date from 23 May to 24 May, when Qatar’s communications office said it detected the QNA hack. The 25 May article is contemporaneous; the 30 May letter gives Qatar’s account of the timing.</t>
-  </si>
-  <si>
     <t>Pompeo: Iran behind attack on Saudi oil facilities that will reduce kingdom's output</t>
   </si>
   <si>
@@ -986,12 +965,6 @@
     <t>https://www.theguardian.com/world/2017/may/26/several-killed-in-attack-on-bus-carrying-coptic-christians-in-egypt</t>
   </si>
   <si>
-    <t>Assigned to the 26 May 2017 raw peak in GPRD_ACT_21_3. Same-day Guardian coverage documents the Minya bus attack on Coptic Christians, an ACT-type event. The Qatar News Agency hack remains a separate episode under E10. Because the GPR index aggregates newspaper reporting, this is an audited event attribution rather than proof that one story alone generated the peak.</t>
-  </si>
-  <si>
-    <t>E39</t>
-  </si>
-  <si>
     <t>Berlin Christmas market attack and manhunt for Anis Amri</t>
   </si>
   <si>
@@ -1008,6 +981,9 @@
   </si>
   <si>
     <t>Assigned to the 21 and 23 December 2016 raw peaks in the 21- and 31-day ACT specifications. The 21 December Guardian report covers the Berlin market attack and manhunt; the 23 December live coverage reports Anis Amri was shot dead in Milan. The Russian ambassador was also assassinated in Ankara on 19 December, so the GPR peak should not be interpreted as proof that the Berlin story alone drove the index.</t>
+  </si>
+  <si>
+    <t>Assigned to the 26 May 2017 raw peak in GPRD_ACT_21_3. Same-day Guardian coverage identifies the Minya bus attack on Coptic Christians as an ACT-type event. This attribution does not prove that the story alone drove the index.</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +993,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1051,6 +1027,11 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -1220,7 +1201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1293,6 +1274,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1309,6 +1293,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1510,9 +1498,11 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" customWidth="1"/>
     <col min="8" max="8" width="11.5546875" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
     <col min="12" max="12" width="11.44140625" customWidth="1"/>
     <col min="13" max="13" width="89" customWidth="1"/>
@@ -1860,11 +1850,11 @@
       </c>
       <c r="L8" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A8)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E08; E09; E10</v>
+        <v>E08; E09; E37</v>
       </c>
       <c r="M8" t="str" cm="1">
         <f t="array" ref="M8">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A8)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
-        <v>Islamic State attacks on Iran's parliament and Khomeini shrine; Qatar diplomatic crisis begins as neighbouring states sever ties; Qatar News Agency hack that preceded the Qatar diplomatic crisis</v>
+        <v>Islamic State attacks on Iran's parliament and Khomeini shrine; Qatar diplomatic crisis begins as neighbouring states sever ties; Minya bus attack on Coptic Christians in Egypt</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.8">
@@ -1904,7 +1894,7 @@
       </c>
       <c r="L9" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A9)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E11; E12</v>
+        <v>E10; E11</v>
       </c>
       <c r="M9" t="str" cm="1">
         <f t="array" ref="M9">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A9)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -1948,7 +1938,7 @@
       </c>
       <c r="L10" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A10)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E13</v>
+        <v>E12</v>
       </c>
       <c r="M10" t="str" cm="1">
         <f t="array" ref="M10">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A10)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -1992,7 +1982,7 @@
       </c>
       <c r="L11" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A11)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E07; E14</v>
+        <v>E07; E13</v>
       </c>
       <c r="M11" t="str" cm="1">
         <f t="array" ref="M11">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A11)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2036,7 +2026,7 @@
       </c>
       <c r="L12" t="str" cm="1">
         <f t="array" ref="L12">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A12)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E15; E05</v>
+        <v>E14; E05</v>
       </c>
       <c r="M12" t="str" cm="1">
         <f t="array" ref="M12">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A12)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2124,7 +2114,7 @@
       </c>
       <c r="L14" t="str" cm="1">
         <f t="array" ref="L14">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A14)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E16</v>
+        <v>E15</v>
       </c>
       <c r="M14" t="str" cm="1">
         <f t="array" ref="M14">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A14)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2168,7 +2158,7 @@
       </c>
       <c r="L15" t="str" cm="1">
         <f t="array" ref="L15">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A15)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E17</v>
+        <v>E16</v>
       </c>
       <c r="M15" t="str" cm="1">
         <f t="array" ref="M15">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A15)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2212,7 +2202,7 @@
       </c>
       <c r="L16" t="str" cm="1">
         <f t="array" ref="L16">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A16)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E07; E14</v>
+        <v>E07; E13</v>
       </c>
       <c r="M16" t="str" cm="1">
         <f t="array" ref="M16">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A16)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2300,7 +2290,7 @@
       </c>
       <c r="L18" t="str" cm="1">
         <f t="array" ref="L18">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A18)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E18; E19</v>
+        <v>E17; E18</v>
       </c>
       <c r="M18" t="str" cm="1">
         <f t="array" ref="M18">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A18)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2344,7 +2334,7 @@
       </c>
       <c r="L19" t="str" cm="1">
         <f t="array" ref="L19">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A19)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E20; E05</v>
+        <v>E19; E05</v>
       </c>
       <c r="M19" t="str" cm="1">
         <f t="array" ref="M19">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A19)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2432,7 +2422,7 @@
       </c>
       <c r="L21" t="str" cm="1">
         <f t="array" ref="L21">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A21)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E17</v>
+        <v>E16</v>
       </c>
       <c r="M21" t="str" cm="1">
         <f t="array" ref="M21">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A21)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2520,7 +2510,7 @@
       </c>
       <c r="L23" t="str" cm="1">
         <f t="array" ref="L23">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A23)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E39; E21</v>
+        <v>E38; E20</v>
       </c>
       <c r="M23" t="str" cm="1">
         <f t="array" ref="M23">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A23)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2564,7 +2554,7 @@
       </c>
       <c r="L24" t="str" cm="1">
         <f t="array" ref="L24">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A24)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E09; E08; E38</v>
+        <v>E09; E08; E37</v>
       </c>
       <c r="M24" t="str" cm="1">
         <f t="array" ref="M24">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A24)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2608,7 +2598,7 @@
       </c>
       <c r="L25" t="str" cm="1">
         <f t="array" ref="L25">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A25)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E22; E06</v>
+        <v>E21; E06</v>
       </c>
       <c r="M25" t="str" cm="1">
         <f t="array" ref="M25">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A25)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2652,7 +2642,7 @@
       </c>
       <c r="L26" t="str" cm="1">
         <f t="array" ref="L26">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A26)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E07; E14</v>
+        <v>E07; E13</v>
       </c>
       <c r="M26" t="str" cm="1">
         <f t="array" ref="M26">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A26)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2696,7 +2686,7 @@
       </c>
       <c r="L27" t="str" cm="1">
         <f t="array" ref="L27">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A27)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E23; E24</v>
+        <v>E22; E23</v>
       </c>
       <c r="M27" t="str" cm="1">
         <f t="array" ref="M27">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A27)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2784,7 +2774,7 @@
       </c>
       <c r="L29" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A29)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E39; E21</v>
+        <v>E38; E20</v>
       </c>
       <c r="M29" t="str" cm="1">
         <f t="array" ref="M29">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A29)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2828,7 +2818,7 @@
       </c>
       <c r="L30" t="str" cm="1">
         <f t="array" ref="L30">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A30)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E25; E26</v>
+        <v>E24; E25</v>
       </c>
       <c r="M30" t="str" cm="1">
         <f t="array" ref="M30">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A30)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2872,7 +2862,7 @@
       </c>
       <c r="L31" t="str" cm="1">
         <f t="array" ref="L31">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A31)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E07; E14</v>
+        <v>E07; E13</v>
       </c>
       <c r="M31" t="str" cm="1">
         <f t="array" ref="M31">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A31)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2916,7 +2906,7 @@
       </c>
       <c r="L32" t="str" cm="1">
         <f t="array" ref="L32">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A32)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E27</v>
+        <v>E26</v>
       </c>
       <c r="M32" t="str" cm="1">
         <f t="array" ref="M32">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A32)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -2960,7 +2950,7 @@
       </c>
       <c r="L33" t="str" cm="1">
         <f t="array" ref="L33">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A33)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E19; E18</v>
+        <v>E18; E17</v>
       </c>
       <c r="M33" t="str" cm="1">
         <f t="array" ref="M33">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A33)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3004,7 +2994,7 @@
       </c>
       <c r="L34" t="str" cm="1">
         <f t="array" ref="L34">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A34)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E05; E20</v>
+        <v>E05; E19</v>
       </c>
       <c r="M34" t="str" cm="1">
         <f t="array" ref="M34">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A34)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3048,7 +3038,7 @@
       </c>
       <c r="L35" t="str" cm="1">
         <f t="array" ref="L35">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A35)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E28</v>
+        <v>E27</v>
       </c>
       <c r="M35" t="str" cm="1">
         <f t="array" ref="M35">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A35)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3092,7 +3082,7 @@
       </c>
       <c r="L36" t="str" cm="1">
         <f t="array" ref="L36">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A36)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E17</v>
+        <v>E16</v>
       </c>
       <c r="M36" t="str" cm="1">
         <f t="array" ref="M36">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A36)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3136,7 +3126,7 @@
       </c>
       <c r="L37" t="str" cm="1">
         <f t="array" ref="L37">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A37)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E29</v>
+        <v>E28</v>
       </c>
       <c r="M37" t="str" cm="1">
         <f t="array" ref="M37">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A37)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3180,7 +3170,7 @@
       </c>
       <c r="L38" t="str" cm="1">
         <f t="array" ref="L38">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A38)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E30; E31; E32</v>
+        <v>E29; E30; E31</v>
       </c>
       <c r="M38" t="str" cm="1">
         <f t="array" ref="M38">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A38)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3268,7 +3258,7 @@
       </c>
       <c r="L40" t="str" cm="1">
         <f t="array" ref="L40">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A40)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E11; E12</v>
+        <v>E10; E11</v>
       </c>
       <c r="M40" t="str" cm="1">
         <f t="array" ref="M40">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A40)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3312,7 +3302,7 @@
       </c>
       <c r="L41" t="str" cm="1">
         <f t="array" ref="L41">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A41)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E14; E33; E34</v>
+        <v>E13; E32; E33</v>
       </c>
       <c r="M41" t="str" cm="1">
         <f t="array" ref="M41">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A41)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3356,7 +3346,7 @@
       </c>
       <c r="L42" t="str" cm="1">
         <f t="array" ref="L42">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A42)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E35; E36</v>
+        <v>E34; E35</v>
       </c>
       <c r="M42" t="str" cm="1">
         <f t="array" ref="M42">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A42)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3400,7 +3390,7 @@
       </c>
       <c r="L43" t="str" cm="1">
         <f t="array" ref="L43">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A43)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E28</v>
+        <v>E27</v>
       </c>
       <c r="M43" t="str" cm="1">
         <f t="array" ref="M43">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A43)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3444,7 +3434,7 @@
       </c>
       <c r="L44" t="str" cm="1">
         <f t="array" ref="L44">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A44)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E37</v>
+        <v>E36</v>
       </c>
       <c r="M44" t="str" cm="1">
         <f t="array" ref="M44">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A44)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3488,7 +3478,7 @@
       </c>
       <c r="L45" t="str" cm="1">
         <f t="array" ref="L45">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A45)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E17</v>
+        <v>E16</v>
       </c>
       <c r="M45" t="str" cm="1">
         <f t="array" ref="M45">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A45)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3532,7 +3522,7 @@
       </c>
       <c r="L46" t="str" cm="1">
         <f t="array" ref="L46">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$I$2:$I$136,('135 Raw Peak Audit'!$A$2:$A$136=$A46)*('135 Raw Peak Audit'!$I$2:$I$136&lt;&gt;""))))</f>
-        <v>E07; E14; E33</v>
+        <v>E07; E13; E32</v>
       </c>
       <c r="M46" t="str" cm="1">
         <f t="array" ref="M46">_xlfn.TEXTJOIN("; ",TRUE,_xlfn.UNIQUE(_xlfn._xlws.FILTER('135 Raw Peak Audit'!$G$2:$G$136,('135 Raw Peak Audit'!$A$2:$A$136=$A46)*('135 Raw Peak Audit'!$G$2:$G$136&lt;&gt;""))))</f>
@@ -3599,13 +3589,13 @@
         <v>88</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="M1" s="21" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="28.8">
@@ -3634,7 +3624,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="4" t="str">
-        <f>IF(G2="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G2,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G2="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G2,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E01</v>
       </c>
       <c r="J2" s="18">
@@ -3681,7 +3671,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="4" t="str">
-        <f>IF(G3="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G3,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G3="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G3,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E02</v>
       </c>
       <c r="J3" s="18">
@@ -3728,7 +3718,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="4" t="str">
-        <f>IF(G4="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G4,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G4="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G4,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E02</v>
       </c>
       <c r="J4" s="18">
@@ -3775,7 +3765,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="4" t="str">
-        <f>IF(G5="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G5,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G5="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G5,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J5" s="18">
@@ -3822,7 +3812,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="4" t="str">
-        <f>IF(G6="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G6,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G6="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G6,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J6" s="18">
@@ -3869,7 +3859,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="4" t="str">
-        <f>IF(G7="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G7,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G7="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G7,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J7" s="18">
@@ -3916,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="4" t="str">
-        <f>IF(G8="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G8,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G8="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G8,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J8" s="18">
@@ -3963,7 +3953,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="str">
-        <f>IF(G9="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G9,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G9="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G9,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J9" s="18">
@@ -4010,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="4" t="str">
-        <f>IF(G10="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G10,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G10="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G10,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J10" s="18">
@@ -4057,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="4" t="str">
-        <f>IF(G11="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G11,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G11="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G11,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J11" s="18">
@@ -4104,7 +4094,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="4" t="str">
-        <f>IF(G12="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G12,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G12="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G12,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J12" s="18">
@@ -4151,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="4" t="str">
-        <f>IF(G13="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G13,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G13="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G13,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J13" s="18">
@@ -4198,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="4" t="str">
-        <f>IF(G14="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G14,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G14="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G14,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J14" s="18">
@@ -4245,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="4" t="str">
-        <f>IF(G15="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G15,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G15="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G15,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J15" s="18">
@@ -4292,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="4" t="str">
-        <f>IF(G16="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G16,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G16="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G16,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J16" s="18">
@@ -4339,7 +4329,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="4" t="str">
-        <f>IF(G17="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G17,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G17="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G17,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J17" s="18">
@@ -4386,7 +4376,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="4" t="str">
-        <f>IF(G18="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G18,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G18="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G18,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J18" s="18">
@@ -4433,7 +4423,7 @@
         <v>2</v>
       </c>
       <c r="I19" s="4" t="str">
-        <f>IF(G19="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G19,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G19="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G19,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J19" s="18">
@@ -4480,7 +4470,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="4" t="str">
-        <f>IF(G20="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G20,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G20="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G20,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E08</v>
       </c>
       <c r="J20" s="18">
@@ -4527,7 +4517,7 @@
         <v>3</v>
       </c>
       <c r="I21" s="4" t="str">
-        <f>IF(G21="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G21,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G21="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G21,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E09</v>
       </c>
       <c r="J21" s="18">
@@ -4548,7 +4538,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="43.2">
+    <row r="22" spans="1:14" ht="28.8">
       <c r="A22" s="11" t="s">
         <v>25</v>
       </c>
@@ -4568,17 +4558,17 @@
         <v>218.06872558593801</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>101</v>
+        <v>299</v>
       </c>
       <c r="H22" cm="1">
         <v>3</v>
       </c>
       <c r="I22" s="4" t="str">
-        <f>IF(G22="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G22,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E10</v>
+        <f>IF(G22="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G22,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E37</v>
       </c>
       <c r="J22" s="18">
-        <v>42879</v>
+        <v>42881</v>
       </c>
       <c r="K22" s="17" t="str">
         <f t="shared" si="0"/>
@@ -4615,14 +4605,14 @@
         <v>253.34211730957</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H23" cm="1">
         <v>2</v>
       </c>
       <c r="I23" s="4" t="str">
-        <f>IF(G23="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G23,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E11</v>
+        <f>IF(G23="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G23,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E10</v>
       </c>
       <c r="J23" s="18">
         <v>43722</v>
@@ -4662,14 +4652,14 @@
         <v>204.31848144531199</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H24" cm="1">
         <v>2</v>
       </c>
       <c r="I24" s="4" t="str">
-        <f>IF(G24="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G24,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E12</v>
+        <f>IF(G24="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G24,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E11</v>
       </c>
       <c r="J24" s="18">
         <v>43747</v>
@@ -4709,14 +4699,14 @@
         <v>193.50186157226599</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H25" cm="1">
         <v>2</v>
       </c>
       <c r="I25" s="4" t="str">
-        <f>IF(G25="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G25,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E12</v>
+        <f>IF(G25="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G25,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E11</v>
       </c>
       <c r="J25" s="18">
         <v>43747</v>
@@ -4762,8 +4752,8 @@
         <v>1</v>
       </c>
       <c r="I26" s="4" t="str">
-        <f>IF(G26="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G26,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E13</v>
+        <f>IF(G26="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G26,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E12</v>
       </c>
       <c r="J26" s="18">
         <v>45068</v>
@@ -4809,8 +4799,8 @@
         <v>1</v>
       </c>
       <c r="I27" s="4" t="str">
-        <f>IF(G27="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G27,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E13</v>
+        <f>IF(G27="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G27,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E12</v>
       </c>
       <c r="J27" s="18">
         <v>45068</v>
@@ -4856,8 +4846,8 @@
         <v>1</v>
       </c>
       <c r="I28" s="4" t="str">
-        <f>IF(G28="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G28,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E13</v>
+        <f>IF(G28="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G28,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E12</v>
       </c>
       <c r="J28" s="18">
         <v>45068</v>
@@ -4903,7 +4893,7 @@
         <v>2</v>
       </c>
       <c r="I29" s="4" t="str">
-        <f>IF(G29="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G29,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G29="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G29,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J29" s="18">
@@ -4950,7 +4940,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="4" t="str">
-        <f>IF(G30="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G30,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G30="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G30,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J30" s="18">
@@ -4991,14 +4981,14 @@
         <v>447.822265625</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H31" cm="1">
         <v>2</v>
       </c>
       <c r="I31" s="4" t="str">
-        <f>IF(G31="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G31,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E14</v>
+        <f>IF(G31="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G31,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E13</v>
       </c>
       <c r="J31" s="18">
         <v>46112</v>
@@ -5038,14 +5028,14 @@
         <v>186.30352783203099</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H32" cm="1">
         <v>2</v>
       </c>
       <c r="I32" s="4" t="str">
-        <f>IF(G32="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G32,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E15</v>
+        <f>IF(G32="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G32,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E14</v>
       </c>
       <c r="J32" s="18">
         <v>44300</v>
@@ -5091,7 +5081,7 @@
         <v>2</v>
       </c>
       <c r="I33" s="4" t="str">
-        <f>IF(G33="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G33,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G33="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G33,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J33" s="18">
@@ -5138,7 +5128,7 @@
         <v>2</v>
       </c>
       <c r="I34" s="4" t="str">
-        <f>IF(G34="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G34,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G34="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G34,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J34" s="18">
@@ -5185,7 +5175,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="str">
-        <f>IF(G35="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G35,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G35="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G35,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J35" s="18">
@@ -5232,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="4" t="str">
-        <f>IF(G36="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G36,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G36="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G36,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J36" s="18">
@@ -5279,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="4" t="str">
-        <f>IF(G37="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G37,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G37="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G37,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J37" s="18">
@@ -5326,8 +5316,8 @@
         <v>1</v>
       </c>
       <c r="I38" s="4" t="str">
-        <f>IF(G38="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G38,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E16</v>
+        <f>IF(G38="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G38,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E15</v>
       </c>
       <c r="J38" s="18">
         <v>45206</v>
@@ -5373,8 +5363,8 @@
         <v>1</v>
       </c>
       <c r="I39" s="4" t="str">
-        <f>IF(G39="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G39,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E16</v>
+        <f>IF(G39="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G39,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E15</v>
       </c>
       <c r="J39" s="18">
         <v>45206</v>
@@ -5420,8 +5410,8 @@
         <v>1</v>
       </c>
       <c r="I40" s="4" t="str">
-        <f>IF(G40="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G40,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E16</v>
+        <f>IF(G40="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G40,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E15</v>
       </c>
       <c r="J40" s="18">
         <v>45206</v>
@@ -5467,8 +5457,8 @@
         <v>1</v>
       </c>
       <c r="I41" s="4" t="str">
-        <f>IF(G41="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G41,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G41="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G41,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J41" s="18">
         <v>45821</v>
@@ -5514,8 +5504,8 @@
         <v>1</v>
       </c>
       <c r="I42" s="4" t="str">
-        <f>IF(G42="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G42,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G42="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G42,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J42" s="18">
         <v>45821</v>
@@ -5561,8 +5551,8 @@
         <v>1</v>
       </c>
       <c r="I43" s="4" t="str">
-        <f>IF(G43="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G43,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G43="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G43,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J43" s="18">
         <v>45821</v>
@@ -5608,7 +5598,7 @@
         <v>2</v>
       </c>
       <c r="I44" s="4" t="str">
-        <f>IF(G44="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G44,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G44="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G44,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J44" s="18">
@@ -5655,7 +5645,7 @@
         <v>2</v>
       </c>
       <c r="I45" s="4" t="str">
-        <f>IF(G45="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G45,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G45="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G45,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J45" s="18">
@@ -5696,14 +5686,14 @@
         <v>447.822265625</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H46" cm="1">
         <v>2</v>
       </c>
       <c r="I46" s="4" t="str">
-        <f>IF(G46="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G46,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E14</v>
+        <f>IF(G46="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G46,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E13</v>
       </c>
       <c r="J46" s="18">
         <v>46112</v>
@@ -5749,7 +5739,7 @@
         <v>2</v>
       </c>
       <c r="I47" s="4" t="str">
-        <f>IF(G47="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G47,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G47="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G47,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J47" s="18">
@@ -5796,7 +5786,7 @@
         <v>2</v>
       </c>
       <c r="I48" s="4" t="str">
-        <f>IF(G48="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G48,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G48="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G48,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J48" s="18">
@@ -5843,7 +5833,7 @@
         <v>2</v>
       </c>
       <c r="I49" s="4" t="str">
-        <f>IF(G49="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G49,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G49="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G49,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J49" s="18">
@@ -5884,14 +5874,14 @@
         <v>339.62139892578102</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H50" cm="1">
         <v>2</v>
       </c>
       <c r="I50" s="4" t="str">
-        <f>IF(G50="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G50,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E18</v>
+        <f>IF(G50="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G50,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E17</v>
       </c>
       <c r="J50" s="18">
         <v>43838</v>
@@ -5931,14 +5921,14 @@
         <v>191.86993662516301</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H51" cm="1">
         <v>2</v>
       </c>
       <c r="I51" s="4" t="str">
-        <f>IF(G51="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G51,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E19</v>
+        <f>IF(G51="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G51,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E18</v>
       </c>
       <c r="J51" s="18">
         <v>43833</v>
@@ -5978,14 +5968,14 @@
         <v>166.78642272949199</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H52" cm="1">
         <v>2</v>
       </c>
       <c r="I52" s="4" t="str">
-        <f>IF(G52="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G52,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E18</v>
+        <f>IF(G52="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G52,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E17</v>
       </c>
       <c r="J52" s="18">
         <v>43838</v>
@@ -6025,14 +6015,14 @@
         <v>131.76544189453099</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H53" cm="1">
         <v>2</v>
       </c>
       <c r="I53" s="4" t="str">
-        <f>IF(G53="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G53,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E20</v>
+        <f>IF(G53="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G53,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E19</v>
       </c>
       <c r="J53" s="18">
         <v>44326</v>
@@ -6078,7 +6068,7 @@
         <v>2</v>
       </c>
       <c r="I54" s="4" t="str">
-        <f>IF(G54="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G54,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G54="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G54,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J54" s="18">
@@ -6119,14 +6109,14 @@
         <v>108.11334991455099</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H55" cm="1">
         <v>2</v>
       </c>
       <c r="I55" s="4" t="str">
-        <f>IF(G55="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G55,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E20</v>
+        <f>IF(G55="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G55,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E19</v>
       </c>
       <c r="J55" s="18">
         <v>44326</v>
@@ -6172,7 +6162,7 @@
         <v>1</v>
       </c>
       <c r="I56" s="4" t="str">
-        <f>IF(G56="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G56,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G56="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G56,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J56" s="18">
@@ -6219,7 +6209,7 @@
         <v>1</v>
       </c>
       <c r="I57" s="4" t="str">
-        <f>IF(G57="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G57,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G57="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G57,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J57" s="18">
@@ -6266,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="I58" s="4" t="str">
-        <f>IF(G58="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G58,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G58="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G58,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J58" s="18">
@@ -6313,8 +6303,8 @@
         <v>1</v>
       </c>
       <c r="I59" s="4" t="str">
-        <f>IF(G59="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G59,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G59="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G59,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J59" s="18">
         <v>45821</v>
@@ -6360,8 +6350,8 @@
         <v>1</v>
       </c>
       <c r="I60" s="4" t="str">
-        <f>IF(G60="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G60,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G60="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G60,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J60" s="18">
         <v>45821</v>
@@ -6407,8 +6397,8 @@
         <v>1</v>
       </c>
       <c r="I61" s="4" t="str">
-        <f>IF(G61="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G61,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G61="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G61,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J61" s="18">
         <v>45821</v>
@@ -6454,7 +6444,7 @@
         <v>2</v>
       </c>
       <c r="I62" s="4" t="str">
-        <f>IF(G62="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G62,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G62="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G62,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J62" s="18">
@@ -6501,7 +6491,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="4" t="str">
-        <f>IF(G63="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G63,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G63="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G63,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J63" s="18">
@@ -6548,7 +6538,7 @@
         <v>2</v>
       </c>
       <c r="I64" s="4" t="str">
-        <f>IF(G64="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G64,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G64="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G64,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J64" s="18">
@@ -6589,14 +6579,14 @@
         <v>311.33465576171898</v>
       </c>
       <c r="G65" s="15" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="H65" cm="1">
         <v>2</v>
       </c>
       <c r="I65" s="4" t="str">
-        <f>IF(G65="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G65,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E39</v>
+        <f>IF(G65="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G65,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E38</v>
       </c>
       <c r="J65" s="18">
         <v>42723</v>
@@ -6642,8 +6632,8 @@
         <v>2</v>
       </c>
       <c r="I66" s="4" t="str">
-        <f>IF(G66="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G66,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E21</v>
+        <f>IF(G66="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G66,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E20</v>
       </c>
       <c r="J66" s="18">
         <v>42717</v>
@@ -6683,14 +6673,14 @@
         <v>246.60563659668</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="H67" cm="1">
         <v>2</v>
       </c>
       <c r="I67" s="4" t="str">
-        <f>IF(G67="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G67,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E39</v>
+        <f>IF(G67="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G67,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E38</v>
       </c>
       <c r="J67" s="18">
         <v>42723</v>
@@ -6736,7 +6726,7 @@
         <v>3</v>
       </c>
       <c r="I68" s="4" t="str">
-        <f>IF(G68="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G68,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G68="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G68,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E09</v>
       </c>
       <c r="J68" s="18">
@@ -6783,7 +6773,7 @@
         <v>3</v>
       </c>
       <c r="I69" s="4" t="str">
-        <f>IF(G69="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G69,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G69="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G69,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E08</v>
       </c>
       <c r="J69" s="18">
@@ -6824,14 +6814,14 @@
         <v>289.86331176757801</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="H70" cm="1">
         <v>3</v>
       </c>
       <c r="I70" s="4" t="str">
-        <f>IF(G70="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G70,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E38</v>
+        <f>IF(G70="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G70,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E37</v>
       </c>
       <c r="J70" s="18">
         <v>42881</v>
@@ -6871,14 +6861,14 @@
         <v>336.85391235351602</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H71" cm="1">
         <v>2</v>
       </c>
       <c r="I71" s="4" t="str">
-        <f>IF(G71="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G71,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E22</v>
+        <f>IF(G71="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G71,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E21</v>
       </c>
       <c r="J71" s="18">
         <v>45707</v>
@@ -6924,7 +6914,7 @@
         <v>2</v>
       </c>
       <c r="I72" s="4" t="str">
-        <f>IF(G72="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G72,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G72="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G72,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J72" s="18">
@@ -6971,7 +6961,7 @@
         <v>2</v>
       </c>
       <c r="I73" s="4" t="str">
-        <f>IF(G73="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G73,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G73="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G73,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E06</v>
       </c>
       <c r="J73" s="18">
@@ -7018,7 +7008,7 @@
         <v>2</v>
       </c>
       <c r="I74" s="4" t="str">
-        <f>IF(G74="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G74,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G74="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G74,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J74" s="18">
@@ -7065,7 +7055,7 @@
         <v>2</v>
       </c>
       <c r="I75" s="4" t="str">
-        <f>IF(G75="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G75,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G75="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G75,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J75" s="18">
@@ -7106,14 +7096,14 @@
         <v>590.88153076171898</v>
       </c>
       <c r="G76" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H76" cm="1">
         <v>2</v>
       </c>
       <c r="I76" s="4" t="str">
-        <f>IF(G76="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G76,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E14</v>
+        <f>IF(G76="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G76,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E13</v>
       </c>
       <c r="J76" s="18">
         <v>46112</v>
@@ -7153,14 +7143,14 @@
         <v>259.009521484375</v>
       </c>
       <c r="G77" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H77" cm="1">
         <v>2</v>
       </c>
       <c r="I77" s="4" t="str">
-        <f>IF(G77="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G77,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E23</v>
+        <f>IF(G77="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G77,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E22</v>
       </c>
       <c r="J77" s="18">
         <v>42017</v>
@@ -7200,14 +7190,14 @@
         <v>258.11636352539102</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H78" cm="1">
         <v>2</v>
       </c>
       <c r="I78" s="4" t="str">
-        <f>IF(G78="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G78,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E24</v>
+        <f>IF(G78="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G78,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E23</v>
       </c>
       <c r="J78" s="18">
         <v>42019</v>
@@ -7247,14 +7237,14 @@
         <v>257.60641479492199</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H79" cm="1">
         <v>2</v>
       </c>
       <c r="I79" s="4" t="str">
-        <f>IF(G79="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G79,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E24</v>
+        <f>IF(G79="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G79,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E23</v>
       </c>
       <c r="J79" s="18">
         <v>42019</v>
@@ -7300,7 +7290,7 @@
         <v>2</v>
       </c>
       <c r="I80" s="4" t="str">
-        <f>IF(G80="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G80,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G80="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G80,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J80" s="18">
@@ -7347,7 +7337,7 @@
         <v>2</v>
       </c>
       <c r="I81" s="4" t="str">
-        <f>IF(G81="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G81,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G81="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G81,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J81" s="18">
@@ -7394,7 +7384,7 @@
         <v>2</v>
       </c>
       <c r="I82" s="4" t="str">
-        <f>IF(G82="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G82,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G82="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G82,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J82" s="18">
@@ -7435,14 +7425,14 @@
         <v>311.33465576171898</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="H83" cm="1">
         <v>2</v>
       </c>
       <c r="I83" s="4" t="str">
-        <f>IF(G83="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G83,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E39</v>
+        <f>IF(G83="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G83,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E38</v>
       </c>
       <c r="J83" s="18">
         <v>42723</v>
@@ -7488,8 +7478,8 @@
         <v>2</v>
       </c>
       <c r="I84" s="4" t="str">
-        <f>IF(G84="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G84,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E21</v>
+        <f>IF(G84="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G84,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E20</v>
       </c>
       <c r="J84" s="18">
         <v>42717</v>
@@ -7529,14 +7519,14 @@
         <v>246.60563659668</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="H85" cm="1">
         <v>2</v>
       </c>
       <c r="I85" s="4" t="str">
-        <f>IF(G85="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G85,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E39</v>
+        <f>IF(G85="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G85,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E38</v>
       </c>
       <c r="J85" s="18">
         <v>42723</v>
@@ -7576,14 +7566,14 @@
         <v>165.32522583007801</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="H86" cm="1">
         <v>2</v>
       </c>
       <c r="I86" s="4" t="str">
-        <f>IF(G86="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G86,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E25</v>
+        <f>IF(G86="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G86,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E24</v>
       </c>
       <c r="J86" s="18">
         <v>43510</v>
@@ -7623,14 +7613,14 @@
         <v>153.59866333007801</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="H87" cm="1">
         <v>2</v>
       </c>
       <c r="I87" s="4" t="str">
-        <f>IF(G87="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G87,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E25</v>
+        <f>IF(G87="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G87,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E24</v>
       </c>
       <c r="J87" s="18">
         <v>43510</v>
@@ -7670,14 +7660,14 @@
         <v>142.805252075195</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="H88" cm="1">
         <v>2</v>
       </c>
       <c r="I88" s="4" t="str">
-        <f>IF(G88="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G88,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E26</v>
+        <f>IF(G88="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G88,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E25</v>
       </c>
       <c r="J88" s="18">
         <v>43539</v>
@@ -7723,7 +7713,7 @@
         <v>2</v>
       </c>
       <c r="I89" s="4" t="str">
-        <f>IF(G89="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G89,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G89="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G89,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J89" s="18">
@@ -7770,7 +7760,7 @@
         <v>2</v>
       </c>
       <c r="I90" s="4" t="str">
-        <f>IF(G90="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G90,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G90="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G90,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J90" s="18">
@@ -7811,14 +7801,14 @@
         <v>590.88153076171898</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H91" cm="1">
         <v>2</v>
       </c>
       <c r="I91" s="4" t="str">
-        <f>IF(G91="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G91,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E14</v>
+        <f>IF(G91="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G91,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E13</v>
       </c>
       <c r="J91" s="18">
         <v>46112</v>
@@ -7864,8 +7854,8 @@
         <v>1</v>
       </c>
       <c r="I92" s="4" t="str">
-        <f>IF(G92="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G92,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E27</v>
+        <f>IF(G92="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G92,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E26</v>
       </c>
       <c r="J92" s="18">
         <v>42375</v>
@@ -7911,8 +7901,8 @@
         <v>1</v>
       </c>
       <c r="I93" s="4" t="str">
-        <f>IF(G93="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G93,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E27</v>
+        <f>IF(G93="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G93,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E26</v>
       </c>
       <c r="J93" s="18">
         <v>42375</v>
@@ -7958,8 +7948,8 @@
         <v>1</v>
       </c>
       <c r="I94" s="4" t="str">
-        <f>IF(G94="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G94,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E27</v>
+        <f>IF(G94="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G94,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E26</v>
       </c>
       <c r="J94" s="18">
         <v>42375</v>
@@ -7999,14 +7989,14 @@
         <v>622.11676025390602</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H95" cm="1">
         <v>2</v>
       </c>
       <c r="I95" s="4" t="str">
-        <f>IF(G95="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G95,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E19</v>
+        <f>IF(G95="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G95,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E18</v>
       </c>
       <c r="J95" s="18">
         <v>43833</v>
@@ -8046,14 +8036,14 @@
         <v>551.646240234375</v>
       </c>
       <c r="G96" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H96" cm="1">
         <v>2</v>
       </c>
       <c r="I96" s="4" t="str">
-        <f>IF(G96="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G96,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E18</v>
+        <f>IF(G96="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G96,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E17</v>
       </c>
       <c r="J96" s="18">
         <v>43838</v>
@@ -8093,14 +8083,14 @@
         <v>320.62907918294297</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H97" cm="1">
         <v>2</v>
       </c>
       <c r="I97" s="4" t="str">
-        <f>IF(G97="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G97,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E19</v>
+        <f>IF(G97="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G97,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E18</v>
       </c>
       <c r="J97" s="18">
         <v>43833</v>
@@ -8146,7 +8136,7 @@
         <v>2</v>
       </c>
       <c r="I98" s="4" t="str">
-        <f>IF(G98="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G98,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G98="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G98,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J98" s="18">
@@ -8193,7 +8183,7 @@
         <v>2</v>
       </c>
       <c r="I99" s="4" t="str">
-        <f>IF(G99="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G99,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G99="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G99,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E05</v>
       </c>
       <c r="J99" s="18">
@@ -8234,14 +8224,14 @@
         <v>204.66900634765599</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H100" cm="1">
         <v>2</v>
       </c>
       <c r="I100" s="4" t="str">
-        <f>IF(G100="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G100,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E20</v>
+        <f>IF(G100="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G100,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E19</v>
       </c>
       <c r="J100" s="18">
         <v>44326</v>
@@ -8287,8 +8277,8 @@
         <v>1</v>
       </c>
       <c r="I101" s="4" t="str">
-        <f>IF(G101="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G101,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E28</v>
+        <f>IF(G101="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G101,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E27</v>
       </c>
       <c r="J101" s="18">
         <v>44616</v>
@@ -8334,8 +8324,8 @@
         <v>1</v>
       </c>
       <c r="I102" s="4" t="str">
-        <f>IF(G102="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G102,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E28</v>
+        <f>IF(G102="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G102,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E27</v>
       </c>
       <c r="J102" s="18">
         <v>44616</v>
@@ -8381,8 +8371,8 @@
         <v>1</v>
       </c>
       <c r="I103" s="4" t="str">
-        <f>IF(G103="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G103,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E28</v>
+        <f>IF(G103="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G103,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E27</v>
       </c>
       <c r="J103" s="18">
         <v>44616</v>
@@ -8428,8 +8418,8 @@
         <v>1</v>
       </c>
       <c r="I104" s="4" t="str">
-        <f>IF(G104="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G104,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G104="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G104,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J104" s="18">
         <v>45821</v>
@@ -8475,8 +8465,8 @@
         <v>1</v>
       </c>
       <c r="I105" s="4" t="str">
-        <f>IF(G105="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G105,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G105="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G105,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J105" s="18">
         <v>45821</v>
@@ -8522,8 +8512,8 @@
         <v>1</v>
       </c>
       <c r="I106" s="4" t="str">
-        <f>IF(G106="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G106,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G106="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G106,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J106" s="18">
         <v>45821</v>
@@ -8569,8 +8559,8 @@
         <v>1</v>
       </c>
       <c r="I107" s="4" t="str">
-        <f>IF(G107="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G107,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E29</v>
+        <f>IF(G107="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G107,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E28</v>
       </c>
       <c r="J107" s="18">
         <v>41702</v>
@@ -8616,8 +8606,8 @@
         <v>1</v>
       </c>
       <c r="I108" s="4" t="str">
-        <f>IF(G108="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G108,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E29</v>
+        <f>IF(G108="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G108,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E28</v>
       </c>
       <c r="J108" s="18">
         <v>41702</v>
@@ -8663,8 +8653,8 @@
         <v>1</v>
       </c>
       <c r="I109" s="4" t="str">
-        <f>IF(G109="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G109,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E29</v>
+        <f>IF(G109="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G109,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E28</v>
       </c>
       <c r="J109" s="18">
         <v>41702</v>
@@ -8704,14 +8694,14 @@
         <v>297.44921875</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H110" cm="1">
         <v>3</v>
       </c>
       <c r="I110" s="4" t="str">
-        <f>IF(G110="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G110,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E30</v>
+        <f>IF(G110="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G110,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E29</v>
       </c>
       <c r="J110" s="18">
         <v>41886</v>
@@ -8751,14 +8741,14 @@
         <v>294.84829711914102</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H111" cm="1">
         <v>3</v>
       </c>
       <c r="I111" s="4" t="str">
-        <f>IF(G111="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G111,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E31</v>
+        <f>IF(G111="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G111,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E30</v>
       </c>
       <c r="J111" s="18">
         <v>41884</v>
@@ -8798,14 +8788,14 @@
         <v>285.30001831054699</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H112" cm="1">
         <v>3</v>
       </c>
       <c r="I112" s="4" t="str">
-        <f>IF(G112="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G112,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E32</v>
+        <f>IF(G112="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G112,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E31</v>
       </c>
       <c r="J112" s="18">
         <v>41859</v>
@@ -8851,7 +8841,7 @@
         <v>2</v>
       </c>
       <c r="I113" s="4" t="str">
-        <f>IF(G113="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G113,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G113="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G113,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E03</v>
       </c>
       <c r="J113" s="18">
@@ -8898,7 +8888,7 @@
         <v>2</v>
       </c>
       <c r="I114" s="4" t="str">
-        <f>IF(G114="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G114,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G114="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G114,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J114" s="18">
@@ -8945,7 +8935,7 @@
         <v>2</v>
       </c>
       <c r="I115" s="4" t="str">
-        <f>IF(G115="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G115,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G115="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G115,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E04</v>
       </c>
       <c r="J115" s="18">
@@ -8986,14 +8976,14 @@
         <v>325.92974853515602</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H116" cm="1">
         <v>2</v>
       </c>
       <c r="I116" s="4" t="str">
-        <f>IF(G116="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G116,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E11</v>
+        <f>IF(G116="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G116,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E10</v>
       </c>
       <c r="J116" s="18">
         <v>43722</v>
@@ -9033,14 +9023,14 @@
         <v>283.49554443359398</v>
       </c>
       <c r="G117" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H117" cm="1">
         <v>2</v>
       </c>
       <c r="I117" s="4" t="str">
-        <f>IF(G117="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G117,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E12</v>
+        <f>IF(G117="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G117,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E11</v>
       </c>
       <c r="J117" s="18">
         <v>43747</v>
@@ -9080,14 +9070,14 @@
         <v>240.13623046875</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H118" cm="1">
         <v>2</v>
       </c>
       <c r="I118" s="4" t="str">
-        <f>IF(G118="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G118,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E11</v>
+        <f>IF(G118="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G118,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E10</v>
       </c>
       <c r="J118" s="18">
         <v>43722</v>
@@ -9127,14 +9117,14 @@
         <v>492.85354614257801</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H119" cm="1">
         <v>3</v>
       </c>
       <c r="I119" s="4" t="str">
-        <f>IF(G119="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G119,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E14</v>
+        <f>IF(G119="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G119,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E13</v>
       </c>
       <c r="J119" s="18">
         <v>46112</v>
@@ -9174,14 +9164,14 @@
         <v>488.78439331054699</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H120" cm="1">
         <v>3</v>
       </c>
       <c r="I120" s="4" t="str">
-        <f>IF(G120="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G120,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E33</v>
+        <f>IF(G120="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G120,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E32</v>
       </c>
       <c r="J120" s="18">
         <v>46120</v>
@@ -9221,14 +9211,14 @@
         <v>475.73468017578102</v>
       </c>
       <c r="G121" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H121" cm="1">
         <v>3</v>
       </c>
       <c r="I121" s="4" t="str">
-        <f>IF(G121="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G121,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E34</v>
+        <f>IF(G121="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G121,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E33</v>
       </c>
       <c r="J121" s="18">
         <v>46125</v>
@@ -9268,14 +9258,14 @@
         <v>330.54043579101602</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H122" cm="1">
         <v>2</v>
       </c>
       <c r="I122" s="4" t="str">
-        <f>IF(G122="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G122,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E35</v>
+        <f>IF(G122="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G122,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E34</v>
       </c>
       <c r="J122" s="18">
         <v>42955</v>
@@ -9315,14 +9305,14 @@
         <v>287.85806274414102</v>
       </c>
       <c r="G123" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H123" cm="1">
         <v>2</v>
       </c>
       <c r="I123" s="4" t="str">
-        <f>IF(G123="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G123,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E36</v>
+        <f>IF(G123="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G123,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E35</v>
       </c>
       <c r="J123" s="18">
         <v>42920</v>
@@ -9362,14 +9352,14 @@
         <v>267.86099243164102</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H124" cm="1">
         <v>2</v>
       </c>
       <c r="I124" s="4" t="str">
-        <f>IF(G124="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G124,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E36</v>
+        <f>IF(G124="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G124,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E35</v>
       </c>
       <c r="J124" s="18">
         <v>42920</v>
@@ -9415,8 +9405,8 @@
         <v>1</v>
       </c>
       <c r="I125" s="4" t="str">
-        <f>IF(G125="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G125,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E28</v>
+        <f>IF(G125="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G125,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E27</v>
       </c>
       <c r="J125" s="18">
         <v>44616</v>
@@ -9462,8 +9452,8 @@
         <v>1</v>
       </c>
       <c r="I126" s="4" t="str">
-        <f>IF(G126="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G126,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E28</v>
+        <f>IF(G126="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G126,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E27</v>
       </c>
       <c r="J126" s="18">
         <v>44616</v>
@@ -9509,8 +9499,8 @@
         <v>1</v>
       </c>
       <c r="I127" s="4" t="str">
-        <f>IF(G127="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G127,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E28</v>
+        <f>IF(G127="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G127,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E27</v>
       </c>
       <c r="J127" s="18">
         <v>44616</v>
@@ -9556,8 +9546,8 @@
         <v>1</v>
       </c>
       <c r="I128" s="4" t="str">
-        <f>IF(G128="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G128,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E37</v>
+        <f>IF(G128="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G128,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E36</v>
       </c>
       <c r="J128" s="18">
         <v>44775</v>
@@ -9603,8 +9593,8 @@
         <v>1</v>
       </c>
       <c r="I129" s="4" t="str">
-        <f>IF(G129="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G129,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E37</v>
+        <f>IF(G129="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G129,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E36</v>
       </c>
       <c r="J129" s="18">
         <v>44775</v>
@@ -9650,8 +9640,8 @@
         <v>1</v>
       </c>
       <c r="I130" s="4" t="str">
-        <f>IF(G130="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G130,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E37</v>
+        <f>IF(G130="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G130,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E36</v>
       </c>
       <c r="J130" s="18">
         <v>44775</v>
@@ -9697,8 +9687,8 @@
         <v>1</v>
       </c>
       <c r="I131" s="4" t="str">
-        <f>IF(G131="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G131,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G131="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G131,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J131" s="18">
         <v>45821</v>
@@ -9744,8 +9734,8 @@
         <v>1</v>
       </c>
       <c r="I132" s="4" t="str">
-        <f>IF(G132="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G132,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G132="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G132,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J132" s="18">
         <v>45821</v>
@@ -9791,8 +9781,8 @@
         <v>1</v>
       </c>
       <c r="I133" s="4" t="str">
-        <f>IF(G133="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G133,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E17</v>
+        <f>IF(G133="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G133,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E16</v>
       </c>
       <c r="J133" s="18">
         <v>45821</v>
@@ -9838,7 +9828,7 @@
         <v>3</v>
       </c>
       <c r="I134" s="4" t="str">
-        <f>IF(G134="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G134,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
+        <f>IF(G134="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G134,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
         <v>E07</v>
       </c>
       <c r="J134" s="18">
@@ -9879,14 +9869,14 @@
         <v>492.85354614257801</v>
       </c>
       <c r="G135" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H135" cm="1">
         <v>3</v>
       </c>
       <c r="I135" s="4" t="str">
-        <f>IF(G135="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G135,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E14</v>
+        <f>IF(G135="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G135,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E13</v>
       </c>
       <c r="J135" s="18">
         <v>46112</v>
@@ -9926,14 +9916,14 @@
         <v>488.78439331054699</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H136" cm="1">
         <v>3</v>
       </c>
       <c r="I136" s="4" t="str">
-        <f>IF(G136="","",IFERROR(INDEX(Sources!$A$2:$A$100,MATCH(G136,Sources!$B$2:$B$100,0)),"MISSING SOURCE"))</f>
-        <v>E33</v>
+        <f>IF(G136="","",IFERROR(INDEX(Sources!$A$2:$A$99,MATCH(G136,Sources!$B$2:$B$99,0)),"MISSING SOURCE"))</f>
+        <v>E32</v>
       </c>
       <c r="J136" s="18">
         <v>46120</v>
@@ -9960,7 +9950,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="45.109375" customWidth="1"/>
@@ -9988,31 +9978,31 @@
         <v>87</v>
       </c>
       <c r="D1" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="F1" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="G1" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="H1" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="I1" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="J1" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="K1" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="K1" s="25" t="s">
+      <c r="L1" s="25" t="s">
         <v>145</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="85.2" customHeight="1">
@@ -10026,23 +10016,23 @@
         <v>42199</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" s="24">
         <v>42199</v>
       </c>
       <c r="F2" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="23" t="s">
         <v>148</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>149</v>
       </c>
       <c r="H2" s="23"/>
       <c r="I2" s="24"/>
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="90.3" customHeight="1">
@@ -10056,23 +10046,23 @@
         <v>42205</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E3" s="24">
         <v>42205</v>
       </c>
       <c r="F3" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="23" t="s">
         <v>152</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>153</v>
       </c>
       <c r="H3" s="23"/>
       <c r="I3" s="24"/>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
       <c r="L3" s="23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="71.7" customHeight="1">
@@ -10086,31 +10076,31 @@
         <v>42321</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E4" s="24">
         <v>42322</v>
       </c>
       <c r="F4" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>156</v>
-      </c>
       <c r="H4" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I4" s="24">
         <v>42326</v>
       </c>
       <c r="J4" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="K4" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="L4" s="23" t="s">
         <v>158</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="70.349999999999994" customHeight="1">
@@ -10124,23 +10114,23 @@
         <v>42332</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E5" s="24">
         <v>42332</v>
       </c>
       <c r="F5" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" s="23" t="s">
         <v>160</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>161</v>
       </c>
       <c r="H5" s="23"/>
       <c r="I5" s="24"/>
       <c r="J5" s="23"/>
       <c r="K5" s="23"/>
       <c r="L5" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="89.85" customHeight="1">
@@ -10154,31 +10144,31 @@
         <v>44337</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E6" s="24">
         <v>44337</v>
       </c>
       <c r="F6" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="H6" s="23" t="s">
         <v>164</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>165</v>
       </c>
       <c r="I6" s="24">
         <v>44372</v>
       </c>
       <c r="J6" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="K6" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="K6" s="23" t="s">
-        <v>167</v>
-      </c>
       <c r="L6" s="23" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="158.4">
@@ -10192,31 +10182,31 @@
         <v>45727</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" s="24">
         <v>45727</v>
       </c>
       <c r="F7" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="G7" s="23" t="s">
-        <v>169</v>
-      </c>
       <c r="H7" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I7" s="24">
         <v>45735</v>
       </c>
       <c r="J7" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="K7" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="L7" s="23" t="s">
         <v>171</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="92.1" customHeight="1">
@@ -10230,31 +10220,31 @@
         <v>46081</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8" s="24">
         <v>46081</v>
       </c>
       <c r="F8" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="G8" s="23" t="s">
-        <v>174</v>
-      </c>
       <c r="H8" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I8" s="24">
         <v>46084</v>
       </c>
       <c r="J8" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="L8" s="23" t="s">
         <v>176</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="67.2" customHeight="1">
@@ -10268,23 +10258,23 @@
         <v>42893</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E9" s="24">
         <v>42893</v>
       </c>
       <c r="F9" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>178</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>179</v>
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="24"/>
       <c r="J9" s="23"/>
       <c r="K9" s="23"/>
       <c r="L9" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="84.9" customHeight="1">
@@ -10298,1030 +10288,993 @@
         <v>42891</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E10" s="24">
         <v>42891</v>
       </c>
       <c r="F10" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>181</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>182</v>
       </c>
       <c r="H10" s="23"/>
       <c r="I10" s="24"/>
       <c r="J10" s="23"/>
       <c r="K10" s="23"/>
       <c r="L10" s="23" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="56.85" customHeight="1">
+      <c r="A11" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="24">
+        <v>43722</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="24">
+        <v>43722</v>
+      </c>
+      <c r="F11" s="23" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="60.75" customHeight="1">
-      <c r="A11" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="24">
-        <v>42879</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="24">
-        <v>42880</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="G11" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="H11" s="23" t="s">
+    </row>
+    <row r="12" spans="1:12" ht="97.95" customHeight="1">
+      <c r="A12" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="24">
+        <v>43747</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="24">
+        <v>43747</v>
+      </c>
+      <c r="F12" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="I11" s="24">
-        <v>42885</v>
-      </c>
-      <c r="J11" s="23" t="s">
+      <c r="G12" s="23" t="s">
         <v>187</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="56.85" customHeight="1">
-      <c r="A12" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="24">
-        <v>43722</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E12" s="24">
-        <v>43722</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>191</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="24"/>
       <c r="J12" s="23"/>
       <c r="K12" s="23"/>
       <c r="L12" s="23" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="79.5" customHeight="1">
+      <c r="A13" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="24">
+        <v>45068</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" s="24">
+        <v>45068</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" s="24">
+        <v>45078</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="K13" s="23" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="97.95" customHeight="1">
-      <c r="A13" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="24">
-        <v>43747</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="24">
-        <v>43747</v>
-      </c>
-      <c r="F13" s="23" t="s">
+      <c r="L13" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="G13" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="79.5" customHeight="1">
+    </row>
+    <row r="14" spans="1:12" ht="51.45" customHeight="1">
       <c r="A14" s="23" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="C14" s="24">
-        <v>45068</v>
+        <v>46112</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E14" s="24">
-        <v>45068</v>
+        <v>46112</v>
       </c>
       <c r="F14" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="H14" s="23"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="G14" s="23" t="s">
+    </row>
+    <row r="15" spans="1:12" ht="43.8" customHeight="1">
+      <c r="A15" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="24">
+        <v>44300</v>
+      </c>
+      <c r="D15" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I14" s="24">
-        <v>45078</v>
-      </c>
-      <c r="J14" s="23" t="s">
+      <c r="E15" s="24">
+        <v>44300</v>
+      </c>
+      <c r="F15" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="G15" s="23" t="s">
         <v>199</v>
-      </c>
-      <c r="L14" s="23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="51.45" customHeight="1">
-      <c r="A15" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="24">
-        <v>46112</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" s="24">
-        <v>46112</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>202</v>
       </c>
       <c r="H15" s="23"/>
       <c r="I15" s="24"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
       <c r="L15" s="23" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="53.1" customHeight="1">
+      <c r="A16" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="24">
+        <v>45206</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="24">
+        <v>45206</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="I16" s="24">
+        <v>45218</v>
+      </c>
+      <c r="J16" s="23" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="43.8" customHeight="1">
-      <c r="A16" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="24">
-        <v>44300</v>
-      </c>
-      <c r="D16" s="23" t="s">
+      <c r="K16" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="E16" s="24">
-        <v>44300</v>
-      </c>
-      <c r="F16" s="23" t="s">
+      <c r="L16" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="G16" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="H16" s="23"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-      <c r="L16" s="23" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="53.1" customHeight="1">
+    </row>
+    <row r="17" spans="1:12" ht="60.3" customHeight="1">
       <c r="A17" s="23" t="s">
         <v>34</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C17" s="24">
-        <v>45206</v>
+        <v>45821</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>147</v>
+        <v>219</v>
       </c>
       <c r="E17" s="24">
-        <v>45206</v>
+        <v>45821</v>
       </c>
       <c r="F17" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="24">
+        <v>45832</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="92.85" customHeight="1">
+      <c r="A18" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="24">
+        <v>43838</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="24">
+        <v>43839</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="24">
+        <v>43841</v>
+      </c>
+      <c r="J18" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="K18" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="H17" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="I17" s="24">
-        <v>45218</v>
-      </c>
-      <c r="J17" s="23" t="s">
+      <c r="L18" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="K17" s="23" t="s">
+    </row>
+    <row r="19" spans="1:12" ht="59.85" customHeight="1">
+      <c r="A19" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="24">
+        <v>43833</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="24">
+        <v>43833</v>
+      </c>
+      <c r="F19" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="L17" s="23" t="s">
+      <c r="G19" s="23" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="60.3" customHeight="1">
-      <c r="A18" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="24">
-        <v>45821</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>226</v>
-      </c>
-      <c r="E18" s="24">
-        <v>45821</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I18" s="24">
-        <v>45832</v>
-      </c>
-      <c r="J18" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="L18" s="23" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="92.85" customHeight="1">
-      <c r="A19" s="23" t="s">
+      <c r="H19" s="23"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="63" customHeight="1">
+      <c r="A20" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="24">
-        <v>43838</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" s="24">
-        <v>43839</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="G19" s="23" t="s">
+      <c r="C20" s="24">
+        <v>44326</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="E20" s="24">
+        <v>44338</v>
+      </c>
+      <c r="F20" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="H19" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I19" s="24">
-        <v>43841</v>
-      </c>
-      <c r="J19" s="23" t="s">
+      <c r="G20" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="K19" s="23" t="s">
+      <c r="H20" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="24">
+        <v>44326</v>
+      </c>
+      <c r="J20" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="L19" s="23" t="s">
+      <c r="K20" s="23" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="59.85" customHeight="1">
-      <c r="A20" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="24">
-        <v>43833</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="24">
-        <v>43833</v>
-      </c>
-      <c r="F20" s="23" t="s">
+      <c r="L20" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="G20" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="H20" s="23"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="63" customHeight="1">
+    </row>
+    <row r="21" spans="1:12" ht="44.85" customHeight="1">
       <c r="A21" s="23" t="s">
         <v>37</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>115</v>
+        <v>48</v>
       </c>
       <c r="C21" s="24">
-        <v>44326</v>
+        <v>42717</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E21" s="24">
-        <v>44338</v>
+        <v>42717</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I21" s="24">
-        <v>44326</v>
+        <v>42734</v>
       </c>
       <c r="J21" s="23" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="44.85" customHeight="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="86.7" customHeight="1">
       <c r="A22" s="23" t="s">
         <v>47</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="C22" s="24">
-        <v>42717</v>
+        <v>45707</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E22" s="24">
-        <v>42717</v>
+        <v>45707</v>
       </c>
       <c r="F22" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="H22" s="23"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="70.349999999999994" customHeight="1">
+      <c r="A23" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="24">
+        <v>42017</v>
+      </c>
+      <c r="D23" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="E23" s="24">
+        <v>42017</v>
+      </c>
+      <c r="F23" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="H22" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I22" s="24">
-        <v>42734</v>
-      </c>
-      <c r="J22" s="23" t="s">
+      <c r="G23" s="23" t="s">
         <v>234</v>
-      </c>
-      <c r="K22" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="L22" s="23" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="86.7" customHeight="1">
-      <c r="A23" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="24">
-        <v>45707</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E23" s="24">
-        <v>45707</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>237</v>
       </c>
       <c r="H23" s="23"/>
       <c r="I23" s="24"/>
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
       <c r="L23" s="23" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="70.349999999999994" customHeight="1">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="67.5" customHeight="1">
       <c r="A24" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B24" s="23" t="s">
-        <v>119</v>
-      </c>
       <c r="C24" s="24">
-        <v>42017</v>
+        <v>42019</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>239</v>
+        <v>146</v>
       </c>
       <c r="E24" s="24">
-        <v>42017</v>
+        <v>42019</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H24" s="23"/>
       <c r="I24" s="24"/>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="23" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="65.7" customHeight="1">
+      <c r="A25" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="24">
+        <v>43510</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="24">
+        <v>43510</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" s="24">
+        <v>43529</v>
+      </c>
+      <c r="J25" s="23" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="67.5" customHeight="1">
-      <c r="A25" s="23" t="s">
+      <c r="K25" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="48" customHeight="1">
+      <c r="A26" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C25" s="24">
-        <v>42019</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" s="24">
-        <v>42019</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="H25" s="23"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="65.7" customHeight="1">
-      <c r="A26" s="23" t="s">
-        <v>123</v>
-      </c>
       <c r="B26" s="23" t="s">
-        <v>246</v>
+        <v>294</v>
       </c>
       <c r="C26" s="24">
-        <v>43510</v>
+        <v>43539</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E26" s="24">
-        <v>43510</v>
+        <v>43539</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>247</v>
+        <v>295</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I26" s="24">
-        <v>43529</v>
+        <v>43543</v>
       </c>
       <c r="J26" s="23" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="48" customHeight="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="48.75" customHeight="1">
       <c r="A27" s="23" t="s">
         <v>58</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>301</v>
+        <v>59</v>
       </c>
       <c r="C27" s="24">
-        <v>43539</v>
+        <v>42375</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
       <c r="E27" s="24">
-        <v>43539</v>
+        <v>42375</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>302</v>
+        <v>245</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I27" s="24">
-        <v>43543</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>298</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>299</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="H27" s="23"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
       <c r="L27" s="23" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="48.75" customHeight="1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="67.95" customHeight="1">
       <c r="A28" s="23" t="s">
         <v>63</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C28" s="24">
-        <v>42375</v>
+        <v>44616</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E28" s="24">
-        <v>42375</v>
+        <v>44616</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H28" s="23"/>
       <c r="I28" s="24"/>
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="67.95" customHeight="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="75.599999999999994" customHeight="1">
       <c r="A29" s="23" t="s">
         <v>67</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C29" s="24">
-        <v>44616</v>
+        <v>41702</v>
       </c>
       <c r="D29" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="24">
+        <v>41702</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" s="24">
+        <v>41716</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="K29" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="E29" s="24">
-        <v>44616</v>
-      </c>
-      <c r="F29" s="23" t="s">
+      <c r="L29" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="G29" s="23" t="s">
+    </row>
+    <row r="30" spans="1:12" ht="51.9" customHeight="1">
+      <c r="A30" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="24">
+        <v>41886</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" s="24">
+        <v>41885</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
-      <c r="L29" s="23" t="s">
+      <c r="G30" s="23" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="75.599999999999994" customHeight="1">
-      <c r="A30" s="23" t="s">
+      <c r="H30" s="23"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="84.45" customHeight="1">
+      <c r="A31" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B30" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="24">
-        <v>41702</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30" s="24">
-        <v>41702</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="G30" s="23" t="s">
+      <c r="C31" s="24">
+        <v>41884</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="24">
+        <v>41884</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="H30" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I30" s="24">
-        <v>41716</v>
-      </c>
-      <c r="J30" s="23" t="s">
+      <c r="G31" s="23" t="s">
         <v>260</v>
-      </c>
-      <c r="K30" s="23" t="s">
-        <v>261</v>
-      </c>
-      <c r="L30" s="23" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="51.9" customHeight="1">
-      <c r="A31" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="C31" s="24">
-        <v>41886</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E31" s="24">
-        <v>41885</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>264</v>
       </c>
       <c r="H31" s="23"/>
       <c r="I31" s="24"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="84.45" customHeight="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="78.75" customHeight="1">
       <c r="A32" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C32" s="24">
-        <v>41884</v>
+        <v>41859</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E32" s="24">
-        <v>41884</v>
+        <v>41859</v>
       </c>
       <c r="F32" s="23" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H32" s="23"/>
       <c r="I32" s="24"/>
       <c r="J32" s="23"/>
       <c r="K32" s="23"/>
       <c r="L32" s="23" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="78.75" customHeight="1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="67.2" customHeight="1">
       <c r="A33" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C33" s="24">
-        <v>41859</v>
+        <v>46120</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E33" s="24">
-        <v>41859</v>
+        <v>46120</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H33" s="23"/>
       <c r="I33" s="24"/>
       <c r="J33" s="23"/>
       <c r="K33" s="23"/>
       <c r="L33" s="23" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="48.3" customHeight="1">
+      <c r="A34" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="24">
+        <v>46125</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="24">
+        <v>46125</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>269</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I34" s="24">
+        <v>46126</v>
+      </c>
+      <c r="J34" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="K34" s="23" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="67.2" customHeight="1">
-      <c r="A34" s="23" t="s">
+      <c r="L34" s="23" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="49.2" customHeight="1">
+      <c r="A35" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B34" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="24">
-        <v>46120</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" s="24">
-        <v>46120</v>
-      </c>
-      <c r="F34" s="23" t="s">
+      <c r="C35" s="24">
+        <v>42955</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E35" s="24">
+        <v>42956</v>
+      </c>
+      <c r="F35" s="23" t="s">
         <v>272</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G35" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="H34" s="23"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="23"/>
-      <c r="K34" s="23"/>
-      <c r="L34" s="23" t="s">
+      <c r="H35" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I35" s="24">
+        <v>42957</v>
+      </c>
+      <c r="J35" s="23" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="48.3" customHeight="1">
-      <c r="A35" s="23" t="s">
+      <c r="K35" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="L35" s="23" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="67.2" customHeight="1">
+      <c r="A36" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B36" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="24">
-        <v>46125</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" s="24">
-        <v>46125</v>
-      </c>
-      <c r="F35" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="G35" s="23" t="s">
+      <c r="C36" s="24">
+        <v>42920</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" s="24">
+        <v>42920</v>
+      </c>
+      <c r="F36" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I35" s="24">
-        <v>46126</v>
-      </c>
-      <c r="J35" s="23" t="s">
+      <c r="G36" s="23" t="s">
         <v>277</v>
       </c>
-      <c r="K35" s="23" t="s">
+      <c r="H36" s="23"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23" t="s">
         <v>278</v>
       </c>
-      <c r="L35" s="23" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="49.2" customHeight="1">
-      <c r="A36" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C36" s="24">
-        <v>42955</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E36" s="24">
-        <v>42956</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="I36" s="24">
-        <v>42957</v>
-      </c>
-      <c r="J36" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="K36" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="L36" s="23" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="67.2" customHeight="1">
+    </row>
+    <row r="37" spans="1:12" ht="72">
       <c r="A37" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C37" s="24">
-        <v>42920</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="E37" s="24">
-        <v>42920</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="H37" s="23"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23" t="s">
+      <c r="B37" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="26">
+        <v>44775</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="26">
+        <v>44775</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="27" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="125.4" customHeight="1">
+      <c r="A38" s="23" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" ht="72">
-      <c r="A38" s="22" t="s">
-        <v>292</v>
-      </c>
       <c r="B38" s="27" t="s">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="C38" s="26">
-        <v>44775</v>
+        <v>42881</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E38" s="26">
-        <v>44775</v>
+        <v>42881</v>
       </c>
       <c r="F38" s="27" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="H38" s="22"/>
       <c r="I38" s="22"/>
       <c r="J38" s="22"/>
       <c r="K38" s="22"/>
-      <c r="L38" s="27" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="187.2">
-      <c r="A39" s="22" t="s">
+      <c r="L38" s="28" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="216">
+      <c r="A39" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C39" s="26">
+        <v>42723</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="26">
+        <v>42725</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="H39" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39" s="22">
+        <v>42727</v>
+      </c>
+      <c r="J39" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="K39" s="22" t="s">
         <v>306</v>
       </c>
-      <c r="C39" s="26">
-        <v>42881</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="26">
-        <v>42881</v>
-      </c>
-      <c r="F39" s="27" t="s">
+      <c r="L39" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="G39" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="27" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="216">
-      <c r="A40" s="22" t="s">
-        <v>310</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="C40" s="26">
-        <v>42723</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="26">
-        <v>42725</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="G40" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="H40" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="I40" s="22">
-        <v>42727</v>
-      </c>
-      <c r="J40" s="22" t="s">
-        <v>314</v>
-      </c>
-      <c r="K40" s="22" t="s">
-        <v>315</v>
-      </c>
-      <c r="L40" s="27" t="s">
-        <v>316</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/GPR_Events.xlsx
+++ b/GPR_Events.xlsx
@@ -17,7 +17,7 @@
     <sheet name="135 Raw Peak Audit" sheetId="2" r:id="rId2"/>
     <sheet name="Sources" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcCompleted="0" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -10171,7 +10171,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="158.4">
+    <row r="7" spans="1:12" ht="172.8">
       <c r="A7" s="23" t="s">
         <v>19</v>
       </c>
